--- a/Assets/Resources/Excel/Entity_GirlLikeSetCompoDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_GirlLikeSetCompoDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBBA67E5-A02A-41CE-AB07-9D60866B50A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FD304E6-7E30-4EF2-82C1-9F1CC069AABB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2520" yWindow="1245" windowWidth="25575" windowHeight="14325" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2835" yWindow="1215" windowWidth="25560" windowHeight="14325" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_Stage1_Set" sheetId="2" r:id="rId1"/>

--- a/Assets/Resources/Excel/Entity_GirlLikeSetCompoDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_GirlLikeSetCompoDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FD304E6-7E30-4EF2-82C1-9F1CC069AABB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F7EE10A-386F-4688-B865-701C3DA98027}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2835" yWindow="1215" windowWidth="25560" windowHeight="14325" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="735" yWindow="735" windowWidth="25560" windowHeight="14325" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_Stage1_Set" sheetId="2" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="172">
   <si>
     <t>desc</t>
   </si>
@@ -1127,19 +1127,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>光の魔法を覚えよう！</t>
-    <rPh sb="0" eb="1">
-      <t>ヒカ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>マホウ</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>オボ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>ヒカリにお菓子を覚えてもらう！</t>
     <rPh sb="5" eb="7">
       <t>カシ</t>
@@ -1154,13 +1141,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>空き～～</t>
-    <rPh sb="0" eb="1">
-      <t>ア</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>かわいいクッキーが食べたい！</t>
     <rPh sb="9" eb="10">
       <t>タ</t>
@@ -1192,6 +1172,47 @@
     </rPh>
     <rPh sb="2" eb="3">
       <t>デ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>＜コンテスト＞</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>クッキー初級コンテストで優勝しよう！</t>
+    <rPh sb="4" eb="6">
+      <t>ショキュウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ユウショウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>プラトンアカデミーコンテストで優勝しよう！</t>
+    <rPh sb="15" eb="17">
+      <t>ユウショウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>女王様と白クジラに会いにいこう！</t>
+    <rPh sb="0" eb="3">
+      <t>ジョオウサマ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>シロ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>エデンを作ろう！</t>
+    <rPh sb="4" eb="5">
+      <t>ツク</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -3843,7 +3864,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0D5A12D-B9F6-41BC-8E5B-D7E79CC788E5}">
-  <dimension ref="A1:P12"/>
+  <dimension ref="A1:P14"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="7" max="7" width="17.28515625" customWidth="1"/>
@@ -3953,7 +3974,7 @@
     </row>
     <row r="3" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
-        <f t="shared" ref="A3:A12" si="0">ROW()-2+1000</f>
+        <f t="shared" ref="A3:A14" si="0">ROW()-2+1000</f>
         <v>1001</v>
       </c>
       <c r="B3" s="2">
@@ -3996,7 +4017,7 @@
         <v>0</v>
       </c>
       <c r="P3" s="14" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -4020,7 +4041,7 @@
         <v>12</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="H4" s="6" t="s">
         <v>54</v>
@@ -4029,7 +4050,7 @@
         <v>54</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="K4" s="4" t="s">
         <v>11</v>
@@ -4047,7 +4068,7 @@
         <v>0</v>
       </c>
       <c r="P4" s="14" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -4059,7 +4080,7 @@
         <v>100030</v>
       </c>
       <c r="C5" s="2">
-        <v>100040</v>
+        <v>100100</v>
       </c>
       <c r="D5" s="2">
         <v>9999</v>
@@ -4071,7 +4092,7 @@
         <v>9999</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="H5" s="6" t="s">
         <v>54</v>
@@ -4083,7 +4104,7 @@
         <v>140</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="L5" s="2">
         <v>0</v>
@@ -4131,7 +4152,7 @@
         <v>37</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>120</v>
+        <v>167</v>
       </c>
       <c r="L6" s="2">
         <v>0</v>
@@ -4158,7 +4179,7 @@
         <v>100110</v>
       </c>
       <c r="D7" s="2">
-        <v>10000</v>
+        <v>9999</v>
       </c>
       <c r="E7" s="2">
         <v>9999</v>
@@ -4167,7 +4188,7 @@
         <v>9999</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="H7" s="6" t="s">
         <v>154</v>
@@ -4179,7 +4200,7 @@
         <v>37</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>121</v>
+        <v>167</v>
       </c>
       <c r="L7" s="2">
         <v>0</v>
@@ -4203,10 +4224,10 @@
         <v>100110</v>
       </c>
       <c r="C8" s="2">
-        <v>100120</v>
+        <v>100400</v>
       </c>
       <c r="D8" s="2">
-        <v>10000</v>
+        <v>9999</v>
       </c>
       <c r="E8" s="2">
         <v>9999</v>
@@ -4215,7 +4236,7 @@
         <v>9999</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="H8" s="6" t="s">
         <v>54</v>
@@ -4227,7 +4248,7 @@
         <v>130</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>121</v>
+        <v>167</v>
       </c>
       <c r="L8" s="2">
         <v>0</v>
@@ -4242,147 +4263,147 @@
         <v>88</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="2">
+    <row r="9" spans="1:16" s="11" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="7">
         <f t="shared" si="0"/>
         <v>1007</v>
       </c>
-      <c r="B9" s="2">
+      <c r="B9" s="7">
         <v>100120</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="7">
         <v>100130</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D9" s="7">
         <v>10000</v>
       </c>
-      <c r="E9" s="2">
-        <v>9999</v>
-      </c>
-      <c r="F9" s="2">
-        <v>9999</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="J9" s="6" t="s">
+      <c r="E9" s="7">
+        <v>9999</v>
+      </c>
+      <c r="F9" s="7">
+        <v>9999</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="J9" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="K9" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="L9" s="2">
-        <v>0</v>
-      </c>
-      <c r="M9" s="2">
-        <v>0</v>
-      </c>
-      <c r="O9" t="b">
-        <v>0</v>
-      </c>
-      <c r="P9" s="14" t="s">
+      <c r="K9" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="L9" s="7">
+        <v>0</v>
+      </c>
+      <c r="M9" s="7">
+        <v>0</v>
+      </c>
+      <c r="O9" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="P9" s="13" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="2">
+    <row r="10" spans="1:16" s="11" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="7">
         <f t="shared" si="0"/>
         <v>1008</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B10" s="7">
         <v>100130</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="7">
         <v>100140</v>
       </c>
-      <c r="D10" s="2">
+      <c r="D10" s="7">
         <v>65</v>
       </c>
-      <c r="E10" s="2">
-        <v>9999</v>
-      </c>
-      <c r="F10" s="2">
-        <v>9999</v>
-      </c>
-      <c r="G10" s="6" t="s">
+      <c r="E10" s="7">
+        <v>9999</v>
+      </c>
+      <c r="F10" s="7">
+        <v>9999</v>
+      </c>
+      <c r="G10" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="H10" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="I10" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="J10" s="6" t="s">
+      <c r="H10" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="J10" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="K10" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="L10" s="2">
-        <v>0</v>
-      </c>
-      <c r="M10" s="2">
-        <v>0</v>
-      </c>
-      <c r="O10" t="b">
-        <v>0</v>
-      </c>
-      <c r="P10" s="14" t="s">
+      <c r="K10" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="L10" s="7">
+        <v>0</v>
+      </c>
+      <c r="M10" s="7">
+        <v>0</v>
+      </c>
+      <c r="O10" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="P10" s="13" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="2">
+    <row r="11" spans="1:16" s="11" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="7">
         <f t="shared" si="0"/>
         <v>1009</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B11" s="7">
         <v>100140</v>
       </c>
-      <c r="C11" s="2">
+      <c r="C11" s="7">
         <v>100500</v>
       </c>
-      <c r="D11" s="2">
+      <c r="D11" s="7">
         <v>10000</v>
       </c>
-      <c r="E11" s="2">
-        <v>9999</v>
-      </c>
-      <c r="F11" s="2">
-        <v>9999</v>
-      </c>
-      <c r="G11" s="6" t="s">
+      <c r="E11" s="7">
+        <v>9999</v>
+      </c>
+      <c r="F11" s="7">
+        <v>9999</v>
+      </c>
+      <c r="G11" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="H11" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="I11" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="J11" s="6" t="s">
+      <c r="H11" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="I11" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="J11" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="K11" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="L11" s="2">
-        <v>0</v>
-      </c>
-      <c r="M11" s="2">
-        <v>0</v>
-      </c>
-      <c r="O11" t="b">
-        <v>0</v>
-      </c>
-      <c r="P11" s="14" t="s">
+      <c r="K11" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="L11" s="7">
+        <v>0</v>
+      </c>
+      <c r="M11" s="7">
+        <v>0</v>
+      </c>
+      <c r="O11" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="P11" s="13" t="s">
         <v>88</v>
       </c>
     </row>
@@ -4392,46 +4413,142 @@
         <v>1010</v>
       </c>
       <c r="B12" s="2">
+        <v>100400</v>
+      </c>
+      <c r="C12" s="2">
+        <v>100410</v>
+      </c>
+      <c r="D12" s="2">
+        <v>9999</v>
+      </c>
+      <c r="E12" s="2">
+        <v>9999</v>
+      </c>
+      <c r="F12" s="2">
+        <v>9999</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="L12" s="2">
+        <v>0</v>
+      </c>
+      <c r="M12" s="2">
+        <v>0</v>
+      </c>
+      <c r="O12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P12" s="14" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="2">
+        <f t="shared" si="0"/>
+        <v>1011</v>
+      </c>
+      <c r="B13" s="2">
+        <v>100410</v>
+      </c>
+      <c r="C13" s="2">
         <v>100500</v>
       </c>
-      <c r="C12" s="2">
-        <v>9999</v>
-      </c>
-      <c r="D12" s="2">
-        <v>9999</v>
-      </c>
-      <c r="E12" s="2">
-        <v>9999</v>
-      </c>
-      <c r="F12" s="2">
-        <v>9999</v>
-      </c>
-      <c r="G12" s="6" t="s">
+      <c r="D13" s="2">
+        <v>9999</v>
+      </c>
+      <c r="E13" s="2">
+        <v>9999</v>
+      </c>
+      <c r="F13" s="2">
+        <v>9999</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="K13" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="L13" s="2">
+        <v>0</v>
+      </c>
+      <c r="M13" s="2">
+        <v>0</v>
+      </c>
+      <c r="O13" t="b">
+        <v>0</v>
+      </c>
+      <c r="P13" s="14" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="2">
+        <f t="shared" si="0"/>
+        <v>1012</v>
+      </c>
+      <c r="B14" s="2">
+        <v>100500</v>
+      </c>
+      <c r="C14" s="2">
+        <v>9999</v>
+      </c>
+      <c r="D14" s="2">
+        <v>9999</v>
+      </c>
+      <c r="E14" s="2">
+        <v>9999</v>
+      </c>
+      <c r="F14" s="2">
+        <v>9999</v>
+      </c>
+      <c r="G14" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="H12" s="6" t="s">
+      <c r="H14" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="I12" s="6" t="s">
+      <c r="I14" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="J12" s="3" t="s">
+      <c r="J14" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="K12" s="4" t="s">
+      <c r="K14" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="L12" s="2">
-        <v>0</v>
-      </c>
-      <c r="M12" s="2">
-        <v>0</v>
-      </c>
-      <c r="N12" s="5"/>
-      <c r="O12" t="b">
-        <v>0</v>
-      </c>
-      <c r="P12" s="14" t="s">
+      <c r="L14" s="2">
+        <v>0</v>
+      </c>
+      <c r="M14" s="2">
+        <v>0</v>
+      </c>
+      <c r="N14" s="5"/>
+      <c r="O14" t="b">
+        <v>0</v>
+      </c>
+      <c r="P14" s="14" t="s">
         <v>74</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_GirlLikeSetCompoDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_GirlLikeSetCompoDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F7EE10A-386F-4688-B865-701C3DA98027}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43431F1D-6292-496C-AF62-7C2602189878}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="735" windowWidth="25560" windowHeight="14325" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3120" yWindow="1875" windowWidth="25560" windowHeight="14325" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_Stage1_Set" sheetId="2" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="177">
   <si>
     <t>desc</t>
   </si>
@@ -1180,16 +1180,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>クッキー初級コンテストで優勝しよう！</t>
-    <rPh sb="4" eb="6">
-      <t>ショキュウ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>ユウショウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>プラトンアカデミーコンテストで優勝しよう！</t>
     <rPh sb="15" eb="17">
       <t>ユウショウ</t>
@@ -1213,6 +1203,60 @@
     <t>エデンを作ろう！</t>
     <rPh sb="4" eb="5">
       <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>春の露店通りへ行ってみよう！</t>
+    <rPh sb="0" eb="1">
+      <t>ハル</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ロテン</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ドオ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>イ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>魔法のおかしを作ってみよう！</t>
+    <rPh sb="0" eb="2">
+      <t>マホウ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>コンテストで優勝しよう！</t>
+    <rPh sb="6" eb="8">
+      <t>ユウショウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>プラトンアカデミーコンテストに出場しよう！</t>
+    <rPh sb="15" eb="17">
+      <t>シュツジョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ようこそ！オランジーナの街へ！</t>
+    <rPh sb="12" eb="13">
+      <t>マチ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>初のコンテスト！</t>
+    <rPh sb="0" eb="1">
+      <t>ハツ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -1264,7 +1308,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1283,6 +1327,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1296,7 +1346,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1316,6 +1366,12 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -3864,7 +3920,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0D5A12D-B9F6-41BC-8E5B-D7E79CC788E5}">
-  <dimension ref="A1:P14"/>
+  <dimension ref="A1:P18"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="7" max="7" width="17.28515625" customWidth="1"/>
@@ -3948,7 +4004,7 @@
         <v>42</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>42</v>
+        <v>175</v>
       </c>
       <c r="I2" s="6" t="s">
         <v>38</v>
@@ -3974,7 +4030,7 @@
     </row>
     <row r="3" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
-        <f t="shared" ref="A3:A14" si="0">ROW()-2+1000</f>
+        <f t="shared" ref="A3:A18" si="0">ROW()-2+1000</f>
         <v>1001</v>
       </c>
       <c r="B3" s="2">
@@ -4119,51 +4175,51 @@
         <v>88</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="2">
+    <row r="6" spans="1:16" s="19" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="15">
         <f t="shared" si="0"/>
         <v>1004</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="15">
         <v>100040</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="15">
         <v>100100</v>
       </c>
-      <c r="D6" s="2">
-        <v>9999</v>
-      </c>
-      <c r="E6" s="2">
-        <v>9999</v>
-      </c>
-      <c r="F6" s="2">
-        <v>9999</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="J6" s="3" t="s">
+      <c r="D6" s="15">
+        <v>9999</v>
+      </c>
+      <c r="E6" s="15">
+        <v>9999</v>
+      </c>
+      <c r="F6" s="15">
+        <v>9999</v>
+      </c>
+      <c r="G6" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="H6" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="I6" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="J6" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="K6" s="4" t="s">
+      <c r="K6" s="18" t="s">
         <v>167</v>
       </c>
-      <c r="L6" s="2">
-        <v>0</v>
-      </c>
-      <c r="M6" s="2">
-        <v>0</v>
-      </c>
-      <c r="O6" t="b">
-        <v>0</v>
-      </c>
-      <c r="P6" s="14" t="s">
+      <c r="L6" s="15">
+        <v>0</v>
+      </c>
+      <c r="M6" s="15">
+        <v>0</v>
+      </c>
+      <c r="O6" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="P6" s="20" t="s">
         <v>88</v>
       </c>
     </row>
@@ -4188,10 +4244,10 @@
         <v>9999</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>154</v>
+        <v>176</v>
       </c>
       <c r="I7" s="6" t="s">
         <v>150</v>
@@ -4224,7 +4280,7 @@
         <v>100110</v>
       </c>
       <c r="C8" s="2">
-        <v>100400</v>
+        <v>100120</v>
       </c>
       <c r="D8" s="2">
         <v>9999</v>
@@ -4236,7 +4292,7 @@
         <v>9999</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="H8" s="6" t="s">
         <v>54</v>
@@ -4244,8 +4300,8 @@
       <c r="I8" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="J8" s="6" t="s">
-        <v>130</v>
+      <c r="J8" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="K8" s="4" t="s">
         <v>167</v>
@@ -4263,147 +4319,147 @@
         <v>88</v>
       </c>
     </row>
-    <row r="9" spans="1:16" s="11" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="7">
+    <row r="9" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="2">
         <f t="shared" si="0"/>
         <v>1007</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9" s="2">
         <v>100120</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9" s="2">
         <v>100130</v>
       </c>
-      <c r="D9" s="7">
-        <v>10000</v>
-      </c>
-      <c r="E9" s="7">
-        <v>9999</v>
-      </c>
-      <c r="F9" s="7">
-        <v>9999</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="H9" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="I9" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="J9" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="K9" s="10" t="s">
+      <c r="D9" s="2">
+        <v>9999</v>
+      </c>
+      <c r="E9" s="2">
+        <v>9999</v>
+      </c>
+      <c r="F9" s="2">
+        <v>9999</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="K9" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="L9" s="7">
-        <v>0</v>
-      </c>
-      <c r="M9" s="7">
-        <v>0</v>
-      </c>
-      <c r="O9" s="11" t="b">
-        <v>0</v>
-      </c>
-      <c r="P9" s="13" t="s">
+      <c r="L9" s="2">
+        <v>0</v>
+      </c>
+      <c r="M9" s="2">
+        <v>0</v>
+      </c>
+      <c r="O9" t="b">
+        <v>0</v>
+      </c>
+      <c r="P9" s="14" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="10" spans="1:16" s="11" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="7">
+    <row r="10" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="2">
         <f t="shared" si="0"/>
         <v>1008</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10" s="2">
         <v>100130</v>
       </c>
-      <c r="C10" s="7">
-        <v>100140</v>
-      </c>
-      <c r="D10" s="7">
-        <v>65</v>
-      </c>
-      <c r="E10" s="7">
-        <v>9999</v>
-      </c>
-      <c r="F10" s="7">
-        <v>9999</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="H10" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="I10" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="J10" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="K10" s="10" t="s">
+      <c r="C10" s="2">
+        <v>100200</v>
+      </c>
+      <c r="D10" s="2">
+        <v>9999</v>
+      </c>
+      <c r="E10" s="2">
+        <v>9999</v>
+      </c>
+      <c r="F10" s="2">
+        <v>9999</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="K10" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="L10" s="7">
-        <v>0</v>
-      </c>
-      <c r="M10" s="7">
-        <v>0</v>
-      </c>
-      <c r="O10" s="11" t="b">
-        <v>0</v>
-      </c>
-      <c r="P10" s="13" t="s">
+      <c r="L10" s="2">
+        <v>0</v>
+      </c>
+      <c r="M10" s="2">
+        <v>0</v>
+      </c>
+      <c r="O10" t="b">
+        <v>0</v>
+      </c>
+      <c r="P10" s="14" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="11" spans="1:16" s="11" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="7">
+    <row r="11" spans="1:16" s="19" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="15">
         <f t="shared" si="0"/>
         <v>1009</v>
       </c>
       <c r="B11" s="7">
-        <v>100140</v>
+        <v>9999</v>
       </c>
       <c r="C11" s="7">
-        <v>100500</v>
-      </c>
-      <c r="D11" s="7">
-        <v>10000</v>
-      </c>
-      <c r="E11" s="7">
-        <v>9999</v>
-      </c>
-      <c r="F11" s="7">
-        <v>9999</v>
-      </c>
-      <c r="G11" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="H11" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="I11" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="J11" s="8" t="s">
-        <v>145</v>
-      </c>
-      <c r="K11" s="10" t="s">
+        <v>9999</v>
+      </c>
+      <c r="D11" s="15">
+        <v>9999</v>
+      </c>
+      <c r="E11" s="15">
+        <v>9999</v>
+      </c>
+      <c r="F11" s="15">
+        <v>9999</v>
+      </c>
+      <c r="G11" s="16" t="s">
+        <v>173</v>
+      </c>
+      <c r="H11" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="I11" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="J11" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="K11" s="18" t="s">
         <v>167</v>
       </c>
-      <c r="L11" s="7">
-        <v>0</v>
-      </c>
-      <c r="M11" s="7">
-        <v>0</v>
-      </c>
-      <c r="O11" s="11" t="b">
-        <v>0</v>
-      </c>
-      <c r="P11" s="13" t="s">
+      <c r="L11" s="15">
+        <v>0</v>
+      </c>
+      <c r="M11" s="15">
+        <v>0</v>
+      </c>
+      <c r="O11" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="P11" s="20" t="s">
         <v>88</v>
       </c>
     </row>
@@ -4413,11 +4469,11 @@
         <v>1010</v>
       </c>
       <c r="B12" s="2">
+        <v>100200</v>
+      </c>
+      <c r="C12" s="2">
         <v>100400</v>
       </c>
-      <c r="C12" s="2">
-        <v>100410</v>
-      </c>
       <c r="D12" s="2">
         <v>9999</v>
       </c>
@@ -4428,16 +4484,16 @@
         <v>9999</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>154</v>
+        <v>54</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>37</v>
+        <v>54</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>130</v>
       </c>
       <c r="K12" s="4" t="s">
         <v>167</v>
@@ -4455,100 +4511,292 @@
         <v>88</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="2">
+    <row r="13" spans="1:16" s="11" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="7">
         <f t="shared" si="0"/>
         <v>1011</v>
       </c>
-      <c r="B13" s="2">
+      <c r="B13" s="7">
+        <v>9999</v>
+      </c>
+      <c r="C13" s="7">
+        <v>9999</v>
+      </c>
+      <c r="D13" s="7">
+        <v>10000</v>
+      </c>
+      <c r="E13" s="7">
+        <v>9999</v>
+      </c>
+      <c r="F13" s="7">
+        <v>9999</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="I13" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="J13" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="K13" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="L13" s="7">
+        <v>0</v>
+      </c>
+      <c r="M13" s="7">
+        <v>0</v>
+      </c>
+      <c r="O13" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="P13" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" s="11" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="7">
+        <f t="shared" si="0"/>
+        <v>1012</v>
+      </c>
+      <c r="B14" s="7">
+        <v>9999</v>
+      </c>
+      <c r="C14" s="7">
+        <v>9999</v>
+      </c>
+      <c r="D14" s="7">
+        <v>65</v>
+      </c>
+      <c r="E14" s="7">
+        <v>9999</v>
+      </c>
+      <c r="F14" s="7">
+        <v>9999</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="I14" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="J14" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="K14" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="L14" s="7">
+        <v>0</v>
+      </c>
+      <c r="M14" s="7">
+        <v>0</v>
+      </c>
+      <c r="O14" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="P14" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" s="11" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="7">
+        <f t="shared" si="0"/>
+        <v>1013</v>
+      </c>
+      <c r="B15" s="7">
+        <v>9999</v>
+      </c>
+      <c r="C15" s="7">
+        <v>9999</v>
+      </c>
+      <c r="D15" s="7">
+        <v>10000</v>
+      </c>
+      <c r="E15" s="7">
+        <v>9999</v>
+      </c>
+      <c r="F15" s="7">
+        <v>9999</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="I15" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="J15" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="K15" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="L15" s="7">
+        <v>0</v>
+      </c>
+      <c r="M15" s="7">
+        <v>0</v>
+      </c>
+      <c r="O15" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="P15" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="2">
+        <f t="shared" si="0"/>
+        <v>1014</v>
+      </c>
+      <c r="B16" s="2">
+        <v>100400</v>
+      </c>
+      <c r="C16" s="2">
         <v>100410</v>
       </c>
-      <c r="C13" s="2">
+      <c r="D16" s="2">
+        <v>9999</v>
+      </c>
+      <c r="E16" s="2">
+        <v>9999</v>
+      </c>
+      <c r="F16" s="2">
+        <v>9999</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="K16" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="L16" s="2">
+        <v>0</v>
+      </c>
+      <c r="M16" s="2">
+        <v>0</v>
+      </c>
+      <c r="O16" t="b">
+        <v>0</v>
+      </c>
+      <c r="P16" s="14" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="2">
+        <f t="shared" si="0"/>
+        <v>1015</v>
+      </c>
+      <c r="B17" s="2">
+        <v>100410</v>
+      </c>
+      <c r="C17" s="2">
         <v>100500</v>
       </c>
-      <c r="D13" s="2">
-        <v>9999</v>
-      </c>
-      <c r="E13" s="2">
-        <v>9999</v>
-      </c>
-      <c r="F13" s="2">
-        <v>9999</v>
-      </c>
-      <c r="G13" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="H13" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="I13" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="J13" s="3" t="s">
+      <c r="D17" s="2">
+        <v>9999</v>
+      </c>
+      <c r="E17" s="2">
+        <v>9999</v>
+      </c>
+      <c r="F17" s="2">
+        <v>9999</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="J17" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="K13" s="4" t="s">
+      <c r="K17" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="L13" s="2">
-        <v>0</v>
-      </c>
-      <c r="M13" s="2">
-        <v>0</v>
-      </c>
-      <c r="O13" t="b">
-        <v>0</v>
-      </c>
-      <c r="P13" s="14" t="s">
+      <c r="L17" s="2">
+        <v>0</v>
+      </c>
+      <c r="M17" s="2">
+        <v>0</v>
+      </c>
+      <c r="O17" t="b">
+        <v>0</v>
+      </c>
+      <c r="P17" s="14" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="2">
-        <f t="shared" si="0"/>
-        <v>1012</v>
-      </c>
-      <c r="B14" s="2">
+    <row r="18" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="2">
+        <f t="shared" si="0"/>
+        <v>1016</v>
+      </c>
+      <c r="B18" s="2">
         <v>100500</v>
       </c>
-      <c r="C14" s="2">
-        <v>9999</v>
-      </c>
-      <c r="D14" s="2">
-        <v>9999</v>
-      </c>
-      <c r="E14" s="2">
-        <v>9999</v>
-      </c>
-      <c r="F14" s="2">
-        <v>9999</v>
-      </c>
-      <c r="G14" s="6" t="s">
+      <c r="C18" s="2">
+        <v>9999</v>
+      </c>
+      <c r="D18" s="2">
+        <v>9999</v>
+      </c>
+      <c r="E18" s="2">
+        <v>9999</v>
+      </c>
+      <c r="F18" s="2">
+        <v>9999</v>
+      </c>
+      <c r="G18" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="H14" s="6" t="s">
+      <c r="H18" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="I14" s="6" t="s">
+      <c r="I18" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="J14" s="3" t="s">
+      <c r="J18" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="K14" s="4" t="s">
+      <c r="K18" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="L14" s="2">
-        <v>0</v>
-      </c>
-      <c r="M14" s="2">
-        <v>0</v>
-      </c>
-      <c r="N14" s="5"/>
-      <c r="O14" t="b">
-        <v>0</v>
-      </c>
-      <c r="P14" s="14" t="s">
+      <c r="L18" s="2">
+        <v>0</v>
+      </c>
+      <c r="M18" s="2">
+        <v>0</v>
+      </c>
+      <c r="N18" s="5"/>
+      <c r="O18" t="b">
+        <v>0</v>
+      </c>
+      <c r="P18" s="14" t="s">
         <v>74</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_GirlLikeSetCompoDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_GirlLikeSetCompoDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43431F1D-6292-496C-AF62-7C2602189878}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{250FEEE0-F6B7-4B66-9862-58701E2B24C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="1875" windowWidth="25560" windowHeight="14325" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2460" yWindow="1275" windowWidth="25560" windowHeight="14325" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_Stage1_Set" sheetId="2" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="179">
   <si>
     <t>desc</t>
   </si>
@@ -1255,6 +1255,20 @@
   </si>
   <si>
     <t>初のコンテスト！</t>
+    <rPh sb="0" eb="1">
+      <t>ハツ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ようこそ！オランジーナの街へ！H</t>
+    <rPh sb="12" eb="13">
+      <t>マチ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>初のコンテスト！H</t>
     <rPh sb="0" eb="1">
       <t>ハツ</t>
     </rPh>
@@ -4007,7 +4021,7 @@
         <v>175</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>38</v>
+        <v>177</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>37</v>
@@ -4250,7 +4264,7 @@
         <v>176</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>150</v>
+        <v>178</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>37</v>

--- a/Assets/Resources/Excel/Entity_GirlLikeSetCompoDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_GirlLikeSetCompoDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{250FEEE0-F6B7-4B66-9862-58701E2B24C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9EB6D21-24D4-4E43-8A49-2EB279EC73C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2460" yWindow="1275" windowWidth="25560" windowHeight="14325" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3240" yWindow="1875" windowWidth="25560" windowHeight="14325" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_Stage1_Set" sheetId="2" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="181">
   <si>
     <t>desc</t>
   </si>
@@ -1180,13 +1180,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>プラトンアカデミーコンテストで優勝しよう！</t>
-    <rPh sb="15" eb="17">
-      <t>ユウショウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>女王様と白クジラに会いにいこう！</t>
     <rPh sb="0" eb="3">
       <t>ジョオウサマ</t>
@@ -1271,6 +1264,30 @@
     <t>初のコンテスト！H</t>
     <rPh sb="0" eb="1">
       <t>ハツ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>お城へ行ってみよう！</t>
+    <rPh sb="1" eb="2">
+      <t>シロ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>イ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>エデンのレシピをゲットしよう！</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>夏コンテストで優勝しよう！</t>
+    <rPh sb="0" eb="1">
+      <t>ナツ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ユウショウ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -3934,7 +3951,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0D5A12D-B9F6-41BC-8E5B-D7E79CC788E5}">
-  <dimension ref="A1:P18"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="7" max="7" width="17.28515625" customWidth="1"/>
@@ -4018,10 +4035,10 @@
         <v>42</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>37</v>
@@ -4044,7 +4061,7 @@
     </row>
     <row r="3" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
-        <f t="shared" ref="A3:A18" si="0">ROW()-2+1000</f>
+        <f t="shared" ref="A3:A19" si="0">ROW()-2+1000</f>
         <v>1001</v>
       </c>
       <c r="B3" s="2">
@@ -4261,10 +4278,10 @@
         <v>159</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>37</v>
@@ -4306,7 +4323,7 @@
         <v>9999</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H8" s="6" t="s">
         <v>54</v>
@@ -4354,7 +4371,7 @@
         <v>9999</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H9" s="6" t="s">
         <v>54</v>
@@ -4402,7 +4419,7 @@
         <v>9999</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>54</v>
@@ -4450,7 +4467,7 @@
         <v>9999</v>
       </c>
       <c r="G11" s="16" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H11" s="16" t="s">
         <v>54</v>
@@ -4486,7 +4503,7 @@
         <v>100200</v>
       </c>
       <c r="C12" s="2">
-        <v>100400</v>
+        <v>100210</v>
       </c>
       <c r="D12" s="2">
         <v>9999</v>
@@ -4498,13 +4515,13 @@
         <v>9999</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>54</v>
+        <v>179</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>54</v>
+        <v>179</v>
       </c>
       <c r="J12" s="6" t="s">
         <v>130</v>
@@ -4525,51 +4542,51 @@
         <v>88</v>
       </c>
     </row>
-    <row r="13" spans="1:16" s="11" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="7">
+    <row r="13" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="2">
         <f t="shared" si="0"/>
         <v>1011</v>
       </c>
-      <c r="B13" s="7">
-        <v>9999</v>
-      </c>
-      <c r="C13" s="7">
-        <v>9999</v>
-      </c>
-      <c r="D13" s="7">
-        <v>10000</v>
-      </c>
-      <c r="E13" s="7">
-        <v>9999</v>
-      </c>
-      <c r="F13" s="7">
-        <v>9999</v>
-      </c>
-      <c r="G13" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="H13" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="I13" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="J13" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="K13" s="10" t="s">
+      <c r="B13" s="2">
+        <v>100210</v>
+      </c>
+      <c r="C13" s="2">
+        <v>100400</v>
+      </c>
+      <c r="D13" s="2">
+        <v>9999</v>
+      </c>
+      <c r="E13" s="2">
+        <v>9999</v>
+      </c>
+      <c r="F13" s="2">
+        <v>9999</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="J13" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="K13" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="L13" s="7">
-        <v>0</v>
-      </c>
-      <c r="M13" s="7">
-        <v>0</v>
-      </c>
-      <c r="O13" s="11" t="b">
-        <v>0</v>
-      </c>
-      <c r="P13" s="13" t="s">
+      <c r="L13" s="2">
+        <v>0</v>
+      </c>
+      <c r="M13" s="2">
+        <v>0</v>
+      </c>
+      <c r="O13" t="b">
+        <v>0</v>
+      </c>
+      <c r="P13" s="14" t="s">
         <v>88</v>
       </c>
     </row>
@@ -4585,7 +4602,7 @@
         <v>9999</v>
       </c>
       <c r="D14" s="7">
-        <v>65</v>
+        <v>10000</v>
       </c>
       <c r="E14" s="7">
         <v>9999</v>
@@ -4594,7 +4611,7 @@
         <v>9999</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>132</v>
+        <v>160</v>
       </c>
       <c r="H14" s="8" t="s">
         <v>54</v>
@@ -4603,7 +4620,7 @@
         <v>54</v>
       </c>
       <c r="J14" s="8" t="s">
-        <v>133</v>
+        <v>95</v>
       </c>
       <c r="K14" s="10" t="s">
         <v>167</v>
@@ -4633,7 +4650,7 @@
         <v>9999</v>
       </c>
       <c r="D15" s="7">
-        <v>10000</v>
+        <v>65</v>
       </c>
       <c r="E15" s="7">
         <v>9999</v>
@@ -4642,7 +4659,7 @@
         <v>9999</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="H15" s="8" t="s">
         <v>54</v>
@@ -4651,7 +4668,7 @@
         <v>54</v>
       </c>
       <c r="J15" s="8" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="K15" s="10" t="s">
         <v>167</v>
@@ -4669,51 +4686,51 @@
         <v>88</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="2">
+    <row r="16" spans="1:16" s="11" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="7">
         <f t="shared" si="0"/>
         <v>1014</v>
       </c>
-      <c r="B16" s="2">
-        <v>100400</v>
-      </c>
-      <c r="C16" s="2">
-        <v>100410</v>
-      </c>
-      <c r="D16" s="2">
-        <v>9999</v>
-      </c>
-      <c r="E16" s="2">
-        <v>9999</v>
-      </c>
-      <c r="F16" s="2">
-        <v>9999</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="I16" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="K16" s="4" t="s">
+      <c r="B16" s="7">
+        <v>9999</v>
+      </c>
+      <c r="C16" s="7">
+        <v>9999</v>
+      </c>
+      <c r="D16" s="7">
+        <v>10000</v>
+      </c>
+      <c r="E16" s="7">
+        <v>9999</v>
+      </c>
+      <c r="F16" s="7">
+        <v>9999</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="I16" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="J16" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="K16" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="L16" s="2">
-        <v>0</v>
-      </c>
-      <c r="M16" s="2">
-        <v>0</v>
-      </c>
-      <c r="O16" t="b">
-        <v>0</v>
-      </c>
-      <c r="P16" s="14" t="s">
+      <c r="L16" s="7">
+        <v>0</v>
+      </c>
+      <c r="M16" s="7">
+        <v>0</v>
+      </c>
+      <c r="O16" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="P16" s="13" t="s">
         <v>88</v>
       </c>
     </row>
@@ -4723,11 +4740,11 @@
         <v>1015</v>
       </c>
       <c r="B17" s="2">
+        <v>100400</v>
+      </c>
+      <c r="C17" s="2">
         <v>100410</v>
       </c>
-      <c r="C17" s="2">
-        <v>100500</v>
-      </c>
       <c r="D17" s="2">
         <v>9999</v>
       </c>
@@ -4738,13 +4755,13 @@
         <v>9999</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>54</v>
+        <v>169</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>54</v>
+        <v>169</v>
       </c>
       <c r="J17" s="3" t="s">
         <v>37</v>
@@ -4771,11 +4788,11 @@
         <v>1016</v>
       </c>
       <c r="B18" s="2">
+        <v>100410</v>
+      </c>
+      <c r="C18" s="2">
         <v>100500</v>
       </c>
-      <c r="C18" s="2">
-        <v>9999</v>
-      </c>
       <c r="D18" s="2">
         <v>9999</v>
       </c>
@@ -4786,31 +4803,79 @@
         <v>9999</v>
       </c>
       <c r="G18" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="K18" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="L18" s="2">
+        <v>0</v>
+      </c>
+      <c r="M18" s="2">
+        <v>0</v>
+      </c>
+      <c r="O18" t="b">
+        <v>0</v>
+      </c>
+      <c r="P18" s="14" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="2">
+        <f t="shared" si="0"/>
+        <v>1017</v>
+      </c>
+      <c r="B19" s="2">
+        <v>100500</v>
+      </c>
+      <c r="C19" s="2">
+        <v>9999</v>
+      </c>
+      <c r="D19" s="2">
+        <v>9999</v>
+      </c>
+      <c r="E19" s="2">
+        <v>9999</v>
+      </c>
+      <c r="F19" s="2">
+        <v>9999</v>
+      </c>
+      <c r="G19" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="H18" s="6" t="s">
+      <c r="H19" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="I18" s="6" t="s">
+      <c r="I19" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="J18" s="3" t="s">
+      <c r="J19" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="K18" s="4" t="s">
+      <c r="K19" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="L18" s="2">
-        <v>0</v>
-      </c>
-      <c r="M18" s="2">
-        <v>0</v>
-      </c>
-      <c r="N18" s="5"/>
-      <c r="O18" t="b">
-        <v>0</v>
-      </c>
-      <c r="P18" s="14" t="s">
+      <c r="L19" s="2">
+        <v>0</v>
+      </c>
+      <c r="M19" s="2">
+        <v>0</v>
+      </c>
+      <c r="N19" s="5"/>
+      <c r="O19" t="b">
+        <v>0</v>
+      </c>
+      <c r="P19" s="14" t="s">
         <v>74</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_GirlLikeSetCompoDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_GirlLikeSetCompoDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9EB6D21-24D4-4E43-8A49-2EB279EC73C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62D99BF1-321A-4F08-88C0-44577C3302AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3240" yWindow="1875" windowWidth="25560" windowHeight="14325" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2085" yWindow="690" windowWidth="25560" windowHeight="14325" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_Stage1_Set" sheetId="2" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="182">
   <si>
     <t>desc</t>
   </si>
@@ -1288,6 +1288,16 @@
     </rPh>
     <rPh sb="7" eb="9">
       <t>ユウショウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>水族館へ行こう！</t>
+    <rPh sb="0" eb="3">
+      <t>スイゾクカン</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>イ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -3951,7 +3961,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0D5A12D-B9F6-41BC-8E5B-D7E79CC788E5}">
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:P20"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="7" max="7" width="17.28515625" customWidth="1"/>
@@ -4061,7 +4071,7 @@
     </row>
     <row r="3" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
-        <f t="shared" ref="A3:A19" si="0">ROW()-2+1000</f>
+        <f t="shared" ref="A3:A20" si="0">ROW()-2+1000</f>
         <v>1001</v>
       </c>
       <c r="B3" s="2">
@@ -4551,7 +4561,7 @@
         <v>100210</v>
       </c>
       <c r="C13" s="2">
-        <v>100400</v>
+        <v>100220</v>
       </c>
       <c r="D13" s="2">
         <v>9999</v>
@@ -4563,7 +4573,7 @@
         <v>9999</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H13" s="6" t="s">
         <v>54</v>
@@ -4590,51 +4600,51 @@
         <v>88</v>
       </c>
     </row>
-    <row r="14" spans="1:16" s="11" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="7">
+    <row r="14" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="2">
         <f t="shared" si="0"/>
         <v>1012</v>
       </c>
-      <c r="B14" s="7">
-        <v>9999</v>
-      </c>
-      <c r="C14" s="7">
-        <v>9999</v>
-      </c>
-      <c r="D14" s="7">
-        <v>10000</v>
-      </c>
-      <c r="E14" s="7">
-        <v>9999</v>
-      </c>
-      <c r="F14" s="7">
-        <v>9999</v>
-      </c>
-      <c r="G14" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="H14" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="I14" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="J14" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="K14" s="10" t="s">
+      <c r="B14" s="2">
+        <v>100220</v>
+      </c>
+      <c r="C14" s="2">
+        <v>100400</v>
+      </c>
+      <c r="D14" s="2">
+        <v>9999</v>
+      </c>
+      <c r="E14" s="2">
+        <v>9999</v>
+      </c>
+      <c r="F14" s="2">
+        <v>9999</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="J14" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="K14" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="L14" s="7">
-        <v>0</v>
-      </c>
-      <c r="M14" s="7">
-        <v>0</v>
-      </c>
-      <c r="O14" s="11" t="b">
-        <v>0</v>
-      </c>
-      <c r="P14" s="13" t="s">
+      <c r="L14" s="2">
+        <v>0</v>
+      </c>
+      <c r="M14" s="2">
+        <v>0</v>
+      </c>
+      <c r="O14" t="b">
+        <v>0</v>
+      </c>
+      <c r="P14" s="14" t="s">
         <v>88</v>
       </c>
     </row>
@@ -4650,7 +4660,7 @@
         <v>9999</v>
       </c>
       <c r="D15" s="7">
-        <v>65</v>
+        <v>10000</v>
       </c>
       <c r="E15" s="7">
         <v>9999</v>
@@ -4659,7 +4669,7 @@
         <v>9999</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>132</v>
+        <v>160</v>
       </c>
       <c r="H15" s="8" t="s">
         <v>54</v>
@@ -4668,7 +4678,7 @@
         <v>54</v>
       </c>
       <c r="J15" s="8" t="s">
-        <v>133</v>
+        <v>95</v>
       </c>
       <c r="K15" s="10" t="s">
         <v>167</v>
@@ -4698,7 +4708,7 @@
         <v>9999</v>
       </c>
       <c r="D16" s="7">
-        <v>10000</v>
+        <v>65</v>
       </c>
       <c r="E16" s="7">
         <v>9999</v>
@@ -4707,7 +4717,7 @@
         <v>9999</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="H16" s="8" t="s">
         <v>54</v>
@@ -4716,7 +4726,7 @@
         <v>54</v>
       </c>
       <c r="J16" s="8" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="K16" s="10" t="s">
         <v>167</v>
@@ -4734,51 +4744,51 @@
         <v>88</v>
       </c>
     </row>
-    <row r="17" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="2">
+    <row r="17" spans="1:16" s="11" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="7">
         <f t="shared" si="0"/>
         <v>1015</v>
       </c>
-      <c r="B17" s="2">
-        <v>100400</v>
-      </c>
-      <c r="C17" s="2">
-        <v>100410</v>
-      </c>
-      <c r="D17" s="2">
-        <v>9999</v>
-      </c>
-      <c r="E17" s="2">
-        <v>9999</v>
-      </c>
-      <c r="F17" s="2">
-        <v>9999</v>
-      </c>
-      <c r="G17" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="H17" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="I17" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="K17" s="4" t="s">
+      <c r="B17" s="7">
+        <v>9999</v>
+      </c>
+      <c r="C17" s="7">
+        <v>9999</v>
+      </c>
+      <c r="D17" s="7">
+        <v>10000</v>
+      </c>
+      <c r="E17" s="7">
+        <v>9999</v>
+      </c>
+      <c r="F17" s="7">
+        <v>9999</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="I17" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="J17" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="K17" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="L17" s="2">
-        <v>0</v>
-      </c>
-      <c r="M17" s="2">
-        <v>0</v>
-      </c>
-      <c r="O17" t="b">
-        <v>0</v>
-      </c>
-      <c r="P17" s="14" t="s">
+      <c r="L17" s="7">
+        <v>0</v>
+      </c>
+      <c r="M17" s="7">
+        <v>0</v>
+      </c>
+      <c r="O17" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="P17" s="13" t="s">
         <v>88</v>
       </c>
     </row>
@@ -4788,11 +4798,11 @@
         <v>1016</v>
       </c>
       <c r="B18" s="2">
+        <v>100400</v>
+      </c>
+      <c r="C18" s="2">
         <v>100410</v>
       </c>
-      <c r="C18" s="2">
-        <v>100500</v>
-      </c>
       <c r="D18" s="2">
         <v>9999</v>
       </c>
@@ -4803,13 +4813,13 @@
         <v>9999</v>
       </c>
       <c r="G18" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="H18" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="H18" s="6" t="s">
-        <v>54</v>
-      </c>
       <c r="I18" s="6" t="s">
-        <v>54</v>
+        <v>169</v>
       </c>
       <c r="J18" s="3" t="s">
         <v>37</v>
@@ -4836,11 +4846,11 @@
         <v>1017</v>
       </c>
       <c r="B19" s="2">
+        <v>100410</v>
+      </c>
+      <c r="C19" s="2">
         <v>100500</v>
       </c>
-      <c r="C19" s="2">
-        <v>9999</v>
-      </c>
       <c r="D19" s="2">
         <v>9999</v>
       </c>
@@ -4851,31 +4861,79 @@
         <v>9999</v>
       </c>
       <c r="G19" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="K19" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="L19" s="2">
+        <v>0</v>
+      </c>
+      <c r="M19" s="2">
+        <v>0</v>
+      </c>
+      <c r="O19" t="b">
+        <v>0</v>
+      </c>
+      <c r="P19" s="14" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="2">
+        <f t="shared" si="0"/>
+        <v>1018</v>
+      </c>
+      <c r="B20" s="2">
+        <v>100500</v>
+      </c>
+      <c r="C20" s="2">
+        <v>9999</v>
+      </c>
+      <c r="D20" s="2">
+        <v>9999</v>
+      </c>
+      <c r="E20" s="2">
+        <v>9999</v>
+      </c>
+      <c r="F20" s="2">
+        <v>9999</v>
+      </c>
+      <c r="G20" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="H19" s="6" t="s">
+      <c r="H20" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="I19" s="6" t="s">
+      <c r="I20" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="J19" s="3" t="s">
+      <c r="J20" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="K19" s="4" t="s">
+      <c r="K20" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="L19" s="2">
-        <v>0</v>
-      </c>
-      <c r="M19" s="2">
-        <v>0</v>
-      </c>
-      <c r="N19" s="5"/>
-      <c r="O19" t="b">
-        <v>0</v>
-      </c>
-      <c r="P19" s="14" t="s">
+      <c r="L20" s="2">
+        <v>0</v>
+      </c>
+      <c r="M20" s="2">
+        <v>0</v>
+      </c>
+      <c r="N20" s="5"/>
+      <c r="O20" t="b">
+        <v>0</v>
+      </c>
+      <c r="P20" s="14" t="s">
         <v>74</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_GirlLikeSetCompoDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_GirlLikeSetCompoDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62D99BF1-321A-4F08-88C0-44577C3302AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72375E76-26B9-42F8-A59D-3299FAB261DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2085" yWindow="690" windowWidth="25560" windowHeight="14325" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2565" yWindow="1275" windowWidth="25560" windowHeight="14325" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_Stage1_Set" sheetId="2" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="184">
   <si>
     <t>desc</t>
   </si>
@@ -1298,6 +1298,23 @@
     </rPh>
     <rPh sb="4" eb="5">
       <t>イ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>秋コンテストで優勝しよう！</t>
+    <rPh sb="0" eb="1">
+      <t>アキ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ユウショウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ままに会いたい</t>
+    <rPh sb="3" eb="4">
+      <t>ア</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -3961,7 +3978,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0D5A12D-B9F6-41BC-8E5B-D7E79CC788E5}">
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="7" max="7" width="17.28515625" customWidth="1"/>
@@ -4071,7 +4088,7 @@
     </row>
     <row r="3" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
-        <f t="shared" ref="A3:A20" si="0">ROW()-2+1000</f>
+        <f t="shared" ref="A3:A21" si="0">ROW()-2+1000</f>
         <v>1001</v>
       </c>
       <c r="B3" s="2">
@@ -4533,8 +4550,8 @@
       <c r="I12" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="J12" s="6" t="s">
-        <v>130</v>
+      <c r="J12" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="K12" s="4" t="s">
         <v>167</v>
@@ -4581,8 +4598,8 @@
       <c r="I13" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="J13" s="6" t="s">
-        <v>130</v>
+      <c r="J13" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="K13" s="4" t="s">
         <v>167</v>
@@ -4609,7 +4626,7 @@
         <v>100220</v>
       </c>
       <c r="C14" s="2">
-        <v>100400</v>
+        <v>100300</v>
       </c>
       <c r="D14" s="2">
         <v>9999</v>
@@ -4629,8 +4646,8 @@
       <c r="I14" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="J14" s="6" t="s">
-        <v>130</v>
+      <c r="J14" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="K14" s="4" t="s">
         <v>167</v>
@@ -4648,51 +4665,51 @@
         <v>88</v>
       </c>
     </row>
-    <row r="15" spans="1:16" s="11" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="7">
+    <row r="15" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="2">
         <f t="shared" si="0"/>
         <v>1013</v>
       </c>
-      <c r="B15" s="7">
-        <v>9999</v>
-      </c>
-      <c r="C15" s="7">
-        <v>9999</v>
-      </c>
-      <c r="D15" s="7">
-        <v>10000</v>
-      </c>
-      <c r="E15" s="7">
-        <v>9999</v>
-      </c>
-      <c r="F15" s="7">
-        <v>9999</v>
-      </c>
-      <c r="G15" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="H15" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="I15" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="J15" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="K15" s="10" t="s">
+      <c r="B15" s="2">
+        <v>100300</v>
+      </c>
+      <c r="C15" s="2">
+        <v>100400</v>
+      </c>
+      <c r="D15" s="2">
+        <v>9999</v>
+      </c>
+      <c r="E15" s="2">
+        <v>9999</v>
+      </c>
+      <c r="F15" s="2">
+        <v>9999</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="K15" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="L15" s="7">
-        <v>0</v>
-      </c>
-      <c r="M15" s="7">
-        <v>0</v>
-      </c>
-      <c r="O15" s="11" t="b">
-        <v>0</v>
-      </c>
-      <c r="P15" s="13" t="s">
+      <c r="L15" s="2">
+        <v>0</v>
+      </c>
+      <c r="M15" s="2">
+        <v>0</v>
+      </c>
+      <c r="O15" t="b">
+        <v>0</v>
+      </c>
+      <c r="P15" s="14" t="s">
         <v>88</v>
       </c>
     </row>
@@ -4708,7 +4725,7 @@
         <v>9999</v>
       </c>
       <c r="D16" s="7">
-        <v>65</v>
+        <v>10000</v>
       </c>
       <c r="E16" s="7">
         <v>9999</v>
@@ -4717,7 +4734,7 @@
         <v>9999</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>132</v>
+        <v>160</v>
       </c>
       <c r="H16" s="8" t="s">
         <v>54</v>
@@ -4726,7 +4743,7 @@
         <v>54</v>
       </c>
       <c r="J16" s="8" t="s">
-        <v>133</v>
+        <v>95</v>
       </c>
       <c r="K16" s="10" t="s">
         <v>167</v>
@@ -4756,7 +4773,7 @@
         <v>9999</v>
       </c>
       <c r="D17" s="7">
-        <v>10000</v>
+        <v>65</v>
       </c>
       <c r="E17" s="7">
         <v>9999</v>
@@ -4765,7 +4782,7 @@
         <v>9999</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="H17" s="8" t="s">
         <v>54</v>
@@ -4774,7 +4791,7 @@
         <v>54</v>
       </c>
       <c r="J17" s="8" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="K17" s="10" t="s">
         <v>167</v>
@@ -4792,51 +4809,51 @@
         <v>88</v>
       </c>
     </row>
-    <row r="18" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="2">
+    <row r="18" spans="1:16" s="11" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="7">
         <f t="shared" si="0"/>
         <v>1016</v>
       </c>
-      <c r="B18" s="2">
-        <v>100400</v>
-      </c>
-      <c r="C18" s="2">
-        <v>100410</v>
-      </c>
-      <c r="D18" s="2">
-        <v>9999</v>
-      </c>
-      <c r="E18" s="2">
-        <v>9999</v>
-      </c>
-      <c r="F18" s="2">
-        <v>9999</v>
-      </c>
-      <c r="G18" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="I18" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="K18" s="4" t="s">
+      <c r="B18" s="7">
+        <v>9999</v>
+      </c>
+      <c r="C18" s="7">
+        <v>9999</v>
+      </c>
+      <c r="D18" s="7">
+        <v>10000</v>
+      </c>
+      <c r="E18" s="7">
+        <v>9999</v>
+      </c>
+      <c r="F18" s="7">
+        <v>9999</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="I18" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="J18" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="K18" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="L18" s="2">
-        <v>0</v>
-      </c>
-      <c r="M18" s="2">
-        <v>0</v>
-      </c>
-      <c r="O18" t="b">
-        <v>0</v>
-      </c>
-      <c r="P18" s="14" t="s">
+      <c r="L18" s="7">
+        <v>0</v>
+      </c>
+      <c r="M18" s="7">
+        <v>0</v>
+      </c>
+      <c r="O18" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="P18" s="13" t="s">
         <v>88</v>
       </c>
     </row>
@@ -4846,11 +4863,11 @@
         <v>1017</v>
       </c>
       <c r="B19" s="2">
+        <v>100400</v>
+      </c>
+      <c r="C19" s="2">
         <v>100410</v>
       </c>
-      <c r="C19" s="2">
-        <v>100500</v>
-      </c>
       <c r="D19" s="2">
         <v>9999</v>
       </c>
@@ -4861,13 +4878,13 @@
         <v>9999</v>
       </c>
       <c r="G19" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="H19" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="H19" s="6" t="s">
-        <v>54</v>
-      </c>
       <c r="I19" s="6" t="s">
-        <v>54</v>
+        <v>183</v>
       </c>
       <c r="J19" s="3" t="s">
         <v>37</v>
@@ -4894,11 +4911,11 @@
         <v>1018</v>
       </c>
       <c r="B20" s="2">
+        <v>100410</v>
+      </c>
+      <c r="C20" s="2">
         <v>100500</v>
       </c>
-      <c r="C20" s="2">
-        <v>9999</v>
-      </c>
       <c r="D20" s="2">
         <v>9999</v>
       </c>
@@ -4909,31 +4926,79 @@
         <v>9999</v>
       </c>
       <c r="G20" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="K20" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="L20" s="2">
+        <v>0</v>
+      </c>
+      <c r="M20" s="2">
+        <v>0</v>
+      </c>
+      <c r="O20" t="b">
+        <v>0</v>
+      </c>
+      <c r="P20" s="14" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="2">
+        <f t="shared" si="0"/>
+        <v>1019</v>
+      </c>
+      <c r="B21" s="2">
+        <v>100500</v>
+      </c>
+      <c r="C21" s="2">
+        <v>9999</v>
+      </c>
+      <c r="D21" s="2">
+        <v>9999</v>
+      </c>
+      <c r="E21" s="2">
+        <v>9999</v>
+      </c>
+      <c r="F21" s="2">
+        <v>9999</v>
+      </c>
+      <c r="G21" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="H20" s="6" t="s">
+      <c r="H21" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="I20" s="6" t="s">
+      <c r="I21" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="J20" s="3" t="s">
+      <c r="J21" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="K20" s="4" t="s">
+      <c r="K21" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="L20" s="2">
-        <v>0</v>
-      </c>
-      <c r="M20" s="2">
-        <v>0</v>
-      </c>
-      <c r="N20" s="5"/>
-      <c r="O20" t="b">
-        <v>0</v>
-      </c>
-      <c r="P20" s="14" t="s">
+      <c r="L21" s="2">
+        <v>0</v>
+      </c>
+      <c r="M21" s="2">
+        <v>0</v>
+      </c>
+      <c r="N21" s="5"/>
+      <c r="O21" t="b">
+        <v>0</v>
+      </c>
+      <c r="P21" s="14" t="s">
         <v>74</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_GirlLikeSetCompoDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_GirlLikeSetCompoDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72375E76-26B9-42F8-A59D-3299FAB261DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E9C2ACB-4696-4E09-A590-2A448C826B90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2565" yWindow="1275" windowWidth="25560" windowHeight="14325" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1590" yWindow="735" windowWidth="25560" windowHeight="14325" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_Stage1_Set" sheetId="2" r:id="rId1"/>
@@ -1254,20 +1254,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>ようこそ！オランジーナの街へ！H</t>
-    <rPh sb="12" eb="13">
-      <t>マチ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>初のコンテスト！H</t>
-    <rPh sb="0" eb="1">
-      <t>ハツ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>お城へ行ってみよう！</t>
     <rPh sb="1" eb="2">
       <t>シロ</t>
@@ -1278,10 +1264,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>エデンのレシピをゲットしよう！</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>夏コンテストで優勝しよう！</t>
     <rPh sb="0" eb="1">
       <t>ナツ</t>
@@ -1315,6 +1297,33 @@
     <t>ままに会いたい</t>
     <rPh sb="3" eb="4">
       <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>初のコンテスト！！</t>
+    <rPh sb="0" eb="1">
+      <t>ハツ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ようこそ！オランジーナの街へ！！</t>
+    <rPh sb="12" eb="13">
+      <t>マチ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>願いを叶えるお菓子！？</t>
+    <rPh sb="0" eb="1">
+      <t>ネガ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>カナ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>カシ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -4065,7 +4074,7 @@
         <v>174</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>37</v>
@@ -4308,7 +4317,7 @@
         <v>175</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>37</v>
@@ -4542,13 +4551,13 @@
         <v>9999</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>37</v>
@@ -4590,7 +4599,7 @@
         <v>9999</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="H13" s="6" t="s">
         <v>54</v>
@@ -4638,7 +4647,7 @@
         <v>9999</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H14" s="6" t="s">
         <v>54</v>
@@ -4686,7 +4695,7 @@
         <v>9999</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="H15" s="6" t="s">
         <v>179</v>
@@ -4884,7 +4893,7 @@
         <v>169</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="J19" s="3" t="s">
         <v>37</v>

--- a/Assets/Resources/Excel/Entity_GirlLikeSetCompoDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_GirlLikeSetCompoDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E9C2ACB-4696-4E09-A590-2A448C826B90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E31D0371-D516-4001-BF25-A9276C452425}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1590" yWindow="735" windowWidth="25560" windowHeight="14325" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="25560" windowHeight="14325" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_Stage1_Set" sheetId="2" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="185">
   <si>
     <t>desc</t>
   </si>
@@ -1216,16 +1216,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>魔法のおかしを作ってみよう！</t>
-    <rPh sb="0" eb="2">
-      <t>マホウ</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>ツク</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>コンテストで優勝しよう！</t>
     <rPh sb="6" eb="8">
       <t>ユウショウ</t>
@@ -1323,6 +1313,23 @@
       <t>カナ</t>
     </rPh>
     <rPh sb="7" eb="9">
+      <t>カシ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>魔法のおかしが食べたい！</t>
+    <rPh sb="0" eb="2">
+      <t>マホウ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>タ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>まほうのお菓子</t>
+    <rPh sb="5" eb="7">
       <t>カシ</t>
     </rPh>
     <phoneticPr fontId="2"/>
@@ -4071,10 +4078,10 @@
         <v>42</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>37</v>
@@ -4314,10 +4321,10 @@
         <v>159</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>37</v>
@@ -4407,7 +4414,7 @@
         <v>9999</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="H9" s="6" t="s">
         <v>54</v>
@@ -4416,7 +4423,7 @@
         <v>54</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>37</v>
+        <v>184</v>
       </c>
       <c r="K9" s="4" t="s">
         <v>167</v>
@@ -4455,7 +4462,7 @@
         <v>9999</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>54</v>
@@ -4503,7 +4510,7 @@
         <v>9999</v>
       </c>
       <c r="G11" s="16" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H11" s="16" t="s">
         <v>54</v>
@@ -4551,13 +4558,13 @@
         <v>9999</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>37</v>
@@ -4599,7 +4606,7 @@
         <v>9999</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H13" s="6" t="s">
         <v>54</v>
@@ -4647,7 +4654,7 @@
         <v>9999</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H14" s="6" t="s">
         <v>54</v>
@@ -4695,13 +4702,13 @@
         <v>9999</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>37</v>
@@ -4893,7 +4900,7 @@
         <v>169</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="J19" s="3" t="s">
         <v>37</v>

--- a/Assets/Resources/Excel/Entity_GirlLikeSetCompoDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_GirlLikeSetCompoDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E31D0371-D516-4001-BF25-A9276C452425}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73062E42-C1C0-4830-A65C-47F43D448D1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="25560" windowHeight="14325" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1890" yWindow="825" windowWidth="25560" windowHeight="14325" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_Stage1_Set" sheetId="2" r:id="rId1"/>
@@ -4354,7 +4354,7 @@
         <v>100110</v>
       </c>
       <c r="C8" s="2">
-        <v>100120</v>
+        <v>100130</v>
       </c>
       <c r="D8" s="2">
         <v>9999</v>

--- a/Assets/Resources/Excel/Entity_GirlLikeSetCompoDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_GirlLikeSetCompoDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73062E42-C1C0-4830-A65C-47F43D448D1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6F76D15-0F3C-4F3F-9B28-27AA258E46B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1890" yWindow="825" windowWidth="25560" windowHeight="14325" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="25560" windowHeight="14355" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_Stage1_Set" sheetId="2" r:id="rId1"/>
@@ -1264,16 +1264,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>水族館へ行こう！</t>
-    <rPh sb="0" eb="3">
-      <t>スイゾクカン</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>イ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>秋コンテストで優勝しよう！</t>
     <rPh sb="0" eb="1">
       <t>アキ</t>
@@ -1331,6 +1321,16 @@
     <t>まほうのお菓子</t>
     <rPh sb="5" eb="7">
       <t>カシ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>各地で、エデンのレシピを集めよう！</t>
+    <rPh sb="0" eb="2">
+      <t>カクチ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>アツ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -4081,7 +4081,7 @@
         <v>173</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>37</v>
@@ -4324,7 +4324,7 @@
         <v>174</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>37</v>
@@ -4414,16 +4414,16 @@
         <v>9999</v>
       </c>
       <c r="G9" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="J9" s="3" t="s">
         <v>183</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>184</v>
       </c>
       <c r="K9" s="4" t="s">
         <v>167</v>
@@ -4561,10 +4561,10 @@
         <v>175</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>37</v>
@@ -4594,7 +4594,7 @@
         <v>100210</v>
       </c>
       <c r="C13" s="2">
-        <v>100220</v>
+        <v>100400</v>
       </c>
       <c r="D13" s="2">
         <v>9999</v>
@@ -4606,7 +4606,7 @@
         <v>9999</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="H13" s="6" t="s">
         <v>54</v>
@@ -4702,13 +4702,13 @@
         <v>9999</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>37</v>
@@ -4900,7 +4900,7 @@
         <v>169</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="J19" s="3" t="s">
         <v>37</v>

--- a/Assets/Resources/Excel/Entity_GirlLikeSetCompoDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_GirlLikeSetCompoDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6F76D15-0F3C-4F3F-9B28-27AA258E46B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA3E0680-67EA-4A9B-9D2E-5D4F1FFF3AC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="25560" windowHeight="14355" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2070" yWindow="1245" windowWidth="25560" windowHeight="14355" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_Stage1_Set" sheetId="2" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="184">
   <si>
     <t>desc</t>
   </si>
@@ -1180,19 +1180,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>女王様と白クジラに会いにいこう！</t>
-    <rPh sb="0" eb="3">
-      <t>ジョオウサマ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>シロ</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>ア</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>エデンを作ろう！</t>
     <rPh sb="4" eb="5">
       <t>ツク</t>
@@ -1254,16 +1241,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>夏コンテストで優勝しよう！</t>
-    <rPh sb="0" eb="1">
-      <t>ナツ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ユウショウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>秋コンテストで優勝しよう！</t>
     <rPh sb="0" eb="1">
       <t>アキ</t>
@@ -1331,6 +1308,16 @@
     </rPh>
     <rPh sb="12" eb="13">
       <t>アツ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>女王様に会いにいこう！</t>
+    <rPh sb="0" eb="3">
+      <t>ジョオウサマ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ア</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -4078,10 +4065,10 @@
         <v>42</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>37</v>
@@ -4321,10 +4308,10 @@
         <v>159</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>37</v>
@@ -4366,7 +4353,7 @@
         <v>9999</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H8" s="6" t="s">
         <v>54</v>
@@ -4414,7 +4401,7 @@
         <v>9999</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H9" s="6" t="s">
         <v>54</v>
@@ -4423,7 +4410,7 @@
         <v>54</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="K9" s="4" t="s">
         <v>167</v>
@@ -4462,7 +4449,7 @@
         <v>9999</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>54</v>
@@ -4510,7 +4497,7 @@
         <v>9999</v>
       </c>
       <c r="G11" s="16" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H11" s="16" t="s">
         <v>54</v>
@@ -4558,13 +4545,13 @@
         <v>9999</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>37</v>
@@ -4594,7 +4581,7 @@
         <v>100210</v>
       </c>
       <c r="C13" s="2">
-        <v>100400</v>
+        <v>100220</v>
       </c>
       <c r="D13" s="2">
         <v>9999</v>
@@ -4606,7 +4593,7 @@
         <v>9999</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H13" s="6" t="s">
         <v>54</v>
@@ -4642,7 +4629,7 @@
         <v>100220</v>
       </c>
       <c r="C14" s="2">
-        <v>100300</v>
+        <v>100400</v>
       </c>
       <c r="D14" s="2">
         <v>9999</v>
@@ -4654,7 +4641,7 @@
         <v>9999</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="H14" s="6" t="s">
         <v>54</v>
@@ -4702,13 +4689,13 @@
         <v>9999</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>37</v>
@@ -4894,13 +4881,13 @@
         <v>9999</v>
       </c>
       <c r="G19" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="H19" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="H19" s="6" t="s">
-        <v>169</v>
-      </c>
       <c r="I19" s="6" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="J19" s="3" t="s">
         <v>37</v>
@@ -4942,7 +4929,7 @@
         <v>9999</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H20" s="6" t="s">
         <v>54</v>

--- a/Assets/Resources/Excel/Entity_GirlLikeSetCompoDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_GirlLikeSetCompoDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA3E0680-67EA-4A9B-9D2E-5D4F1FFF3AC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74B81AB7-B412-40A6-BD52-C2552174970E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2070" yWindow="1245" windowWidth="25560" windowHeight="14355" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="25560" windowHeight="14355" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_Stage1_Set" sheetId="2" r:id="rId1"/>
@@ -1210,114 +1210,114 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
+    <t>ようこそ！オランジーナの街へ！</t>
+    <rPh sb="12" eb="13">
+      <t>マチ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>初のコンテスト！</t>
+    <rPh sb="0" eb="1">
+      <t>ハツ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>お城へ行ってみよう！</t>
+    <rPh sb="1" eb="2">
+      <t>シロ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>イ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>秋コンテストで優勝しよう！</t>
+    <rPh sb="0" eb="1">
+      <t>アキ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ユウショウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ままに会いたい</t>
+    <rPh sb="3" eb="4">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>初のコンテスト！！</t>
+    <rPh sb="0" eb="1">
+      <t>ハツ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ようこそ！オランジーナの街へ！！</t>
+    <rPh sb="12" eb="13">
+      <t>マチ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>願いを叶えるお菓子！？</t>
+    <rPh sb="0" eb="1">
+      <t>ネガ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>カナ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>カシ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>まほうのお菓子</t>
+    <rPh sb="5" eb="7">
+      <t>カシ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>各地で、エデンのレシピを集めよう！</t>
+    <rPh sb="0" eb="2">
+      <t>カクチ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>アツ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>女王様に会いにいこう！</t>
+    <rPh sb="0" eb="3">
+      <t>ジョオウサマ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>魔法のおかしを作ろう！</t>
+    <rPh sb="0" eb="2">
+      <t>マホウ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
     <t>プラトンアカデミーコンテストに出場しよう！</t>
     <rPh sb="15" eb="17">
       <t>シュツジョウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>ようこそ！オランジーナの街へ！</t>
-    <rPh sb="12" eb="13">
-      <t>マチ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>初のコンテスト！</t>
-    <rPh sb="0" eb="1">
-      <t>ハツ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>お城へ行ってみよう！</t>
-    <rPh sb="1" eb="2">
-      <t>シロ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>イ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>秋コンテストで優勝しよう！</t>
-    <rPh sb="0" eb="1">
-      <t>アキ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ユウショウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>ままに会いたい</t>
-    <rPh sb="3" eb="4">
-      <t>ア</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>初のコンテスト！！</t>
-    <rPh sb="0" eb="1">
-      <t>ハツ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>ようこそ！オランジーナの街へ！！</t>
-    <rPh sb="12" eb="13">
-      <t>マチ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>願いを叶えるお菓子！？</t>
-    <rPh sb="0" eb="1">
-      <t>ネガ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>カナ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>カシ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>魔法のおかしが食べたい！</t>
-    <rPh sb="0" eb="2">
-      <t>マホウ</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>タ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>まほうのお菓子</t>
-    <rPh sb="5" eb="7">
-      <t>カシ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>各地で、エデンのレシピを集めよう！</t>
-    <rPh sb="0" eb="2">
-      <t>カクチ</t>
-    </rPh>
-    <rPh sb="12" eb="13">
-      <t>アツ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>女王様に会いにいこう！</t>
-    <rPh sb="0" eb="3">
-      <t>ジョオウサマ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>ア</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -4065,10 +4065,10 @@
         <v>42</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>37</v>
@@ -4308,10 +4308,10 @@
         <v>159</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>37</v>
@@ -4341,7 +4341,7 @@
         <v>100110</v>
       </c>
       <c r="C8" s="2">
-        <v>100130</v>
+        <v>100120</v>
       </c>
       <c r="D8" s="2">
         <v>9999</v>
@@ -4401,7 +4401,7 @@
         <v>9999</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="H9" s="6" t="s">
         <v>54</v>
@@ -4410,7 +4410,7 @@
         <v>54</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="K9" s="4" t="s">
         <v>167</v>
@@ -4449,7 +4449,7 @@
         <v>9999</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>54</v>
@@ -4545,13 +4545,13 @@
         <v>9999</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>37</v>
@@ -4593,7 +4593,7 @@
         <v>9999</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H13" s="6" t="s">
         <v>54</v>
@@ -4641,7 +4641,7 @@
         <v>9999</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H14" s="6" t="s">
         <v>54</v>
@@ -4689,13 +4689,13 @@
         <v>9999</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>37</v>
@@ -4881,13 +4881,13 @@
         <v>9999</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H19" s="6" t="s">
         <v>168</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J19" s="3" t="s">
         <v>37</v>

--- a/Assets/Resources/Excel/Entity_GirlLikeSetCompoDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_GirlLikeSetCompoDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74B81AB7-B412-40A6-BD52-C2552174970E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B8E9A43-2A47-444E-8E8C-81F641FDC1A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="25560" windowHeight="14355" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2895" yWindow="765" windowWidth="25560" windowHeight="14355" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_Stage1_Set" sheetId="2" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="186">
   <si>
     <t>desc</t>
   </si>
@@ -1318,6 +1318,26 @@
     <t>プラトンアカデミーコンテストに出場しよう！</t>
     <rPh sb="15" eb="17">
       <t>シュツジョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>3番目のレシピを集めよう！</t>
+    <rPh sb="1" eb="3">
+      <t>バンメ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>アツ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>白クジラさんに会いにいこう！</t>
+    <rPh sb="0" eb="1">
+      <t>シロ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ア</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -3981,7 +4001,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0D5A12D-B9F6-41BC-8E5B-D7E79CC788E5}">
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:P22"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="7" max="7" width="17.28515625" customWidth="1"/>
@@ -4091,7 +4111,7 @@
     </row>
     <row r="3" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
-        <f t="shared" ref="A3:A21" si="0">ROW()-2+1000</f>
+        <f t="shared" ref="A3:A22" si="0">ROW()-2+1000</f>
         <v>1001</v>
       </c>
       <c r="B3" s="2">
@@ -4641,7 +4661,7 @@
         <v>9999</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="H14" s="6" t="s">
         <v>54</v>
@@ -4917,7 +4937,7 @@
         <v>100410</v>
       </c>
       <c r="C20" s="2">
-        <v>100500</v>
+        <v>100420</v>
       </c>
       <c r="D20" s="2">
         <v>9999</v>
@@ -4929,7 +4949,7 @@
         <v>9999</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>168</v>
+        <v>185</v>
       </c>
       <c r="H20" s="6" t="s">
         <v>54</v>
@@ -4962,11 +4982,11 @@
         <v>1019</v>
       </c>
       <c r="B21" s="2">
+        <v>100420</v>
+      </c>
+      <c r="C21" s="2">
         <v>100500</v>
       </c>
-      <c r="C21" s="2">
-        <v>9999</v>
-      </c>
       <c r="D21" s="2">
         <v>9999</v>
       </c>
@@ -4977,31 +4997,79 @@
         <v>9999</v>
       </c>
       <c r="G21" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="H21" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="K21" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="L21" s="2">
+        <v>0</v>
+      </c>
+      <c r="M21" s="2">
+        <v>0</v>
+      </c>
+      <c r="O21" t="b">
+        <v>0</v>
+      </c>
+      <c r="P21" s="14" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="2">
+        <f t="shared" si="0"/>
+        <v>1020</v>
+      </c>
+      <c r="B22" s="2">
+        <v>100500</v>
+      </c>
+      <c r="C22" s="2">
+        <v>9999</v>
+      </c>
+      <c r="D22" s="2">
+        <v>9999</v>
+      </c>
+      <c r="E22" s="2">
+        <v>9999</v>
+      </c>
+      <c r="F22" s="2">
+        <v>9999</v>
+      </c>
+      <c r="G22" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="H21" s="6" t="s">
+      <c r="H22" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="I21" s="6" t="s">
+      <c r="I22" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="J21" s="3" t="s">
+      <c r="J22" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="K21" s="4" t="s">
+      <c r="K22" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="L21" s="2">
-        <v>0</v>
-      </c>
-      <c r="M21" s="2">
-        <v>0</v>
-      </c>
-      <c r="N21" s="5"/>
-      <c r="O21" t="b">
-        <v>0</v>
-      </c>
-      <c r="P21" s="14" t="s">
+      <c r="L22" s="2">
+        <v>0</v>
+      </c>
+      <c r="M22" s="2">
+        <v>0</v>
+      </c>
+      <c r="N22" s="5"/>
+      <c r="O22" t="b">
+        <v>0</v>
+      </c>
+      <c r="P22" s="14" t="s">
         <v>74</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_GirlLikeSetCompoDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_GirlLikeSetCompoDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B8E9A43-2A47-444E-8E8C-81F641FDC1A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EBF711D-3D5D-4F16-B442-A3D27967F4DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2895" yWindow="765" windowWidth="25560" windowHeight="14355" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2520" yWindow="660" windowWidth="25560" windowHeight="14355" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_Stage1_Set" sheetId="2" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="187">
   <si>
     <t>desc</t>
   </si>
@@ -1315,13 +1315,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>プラトンアカデミーコンテストに出場しよう！</t>
-    <rPh sb="15" eb="17">
-      <t>シュツジョウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>3番目のレシピを集めよう！</t>
     <rPh sb="1" eb="3">
       <t>バンメ</t>
@@ -1338,6 +1331,26 @@
     </rPh>
     <rPh sb="7" eb="8">
       <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>クッキーコンテストで２位以上を取ろう！</t>
+    <rPh sb="11" eb="12">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>イジョウ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ト</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>プラトンアカデミーコンテストで優勝しよう！</t>
+    <rPh sb="15" eb="17">
+      <t>ユウショウ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -4001,7 +4014,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0D5A12D-B9F6-41BC-8E5B-D7E79CC788E5}">
-  <dimension ref="A1:P22"/>
+  <dimension ref="A1:P23"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="7" max="7" width="17.28515625" customWidth="1"/>
@@ -4111,7 +4124,7 @@
     </row>
     <row r="3" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
-        <f t="shared" ref="A3:A22" si="0">ROW()-2+1000</f>
+        <f t="shared" ref="A3:A23" si="0">ROW()-2+1000</f>
         <v>1001</v>
       </c>
       <c r="B3" s="2">
@@ -4457,7 +4470,7 @@
         <v>100130</v>
       </c>
       <c r="C10" s="2">
-        <v>100200</v>
+        <v>100140</v>
       </c>
       <c r="D10" s="2">
         <v>9999</v>
@@ -4469,7 +4482,7 @@
         <v>9999</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>54</v>
@@ -4496,99 +4509,99 @@
         <v>88</v>
       </c>
     </row>
-    <row r="11" spans="1:16" s="19" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="15">
+    <row r="11" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="2">
         <f t="shared" si="0"/>
         <v>1009</v>
       </c>
-      <c r="B11" s="7">
-        <v>9999</v>
-      </c>
-      <c r="C11" s="7">
-        <v>9999</v>
-      </c>
-      <c r="D11" s="15">
-        <v>9999</v>
-      </c>
-      <c r="E11" s="15">
-        <v>9999</v>
-      </c>
-      <c r="F11" s="15">
-        <v>9999</v>
-      </c>
-      <c r="G11" s="16" t="s">
+      <c r="B11" s="2">
+        <v>100140</v>
+      </c>
+      <c r="C11" s="2">
+        <v>100200</v>
+      </c>
+      <c r="D11" s="2">
+        <v>9999</v>
+      </c>
+      <c r="E11" s="2">
+        <v>9999</v>
+      </c>
+      <c r="F11" s="2">
+        <v>9999</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="L11" s="2">
+        <v>0</v>
+      </c>
+      <c r="M11" s="2">
+        <v>0</v>
+      </c>
+      <c r="O11" t="b">
+        <v>0</v>
+      </c>
+      <c r="P11" s="14" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" s="19" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="15">
+        <f t="shared" si="0"/>
+        <v>1010</v>
+      </c>
+      <c r="B12" s="7">
+        <v>9999</v>
+      </c>
+      <c r="C12" s="7">
+        <v>9999</v>
+      </c>
+      <c r="D12" s="15">
+        <v>9999</v>
+      </c>
+      <c r="E12" s="15">
+        <v>9999</v>
+      </c>
+      <c r="F12" s="15">
+        <v>9999</v>
+      </c>
+      <c r="G12" s="16" t="s">
         <v>170</v>
       </c>
-      <c r="H11" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="I11" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="J11" s="17" t="s">
+      <c r="H12" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="I12" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="J12" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="K11" s="18" t="s">
+      <c r="K12" s="18" t="s">
         <v>167</v>
       </c>
-      <c r="L11" s="15">
-        <v>0</v>
-      </c>
-      <c r="M11" s="15">
-        <v>0</v>
-      </c>
-      <c r="O11" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="P11" s="20" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="2">
-        <f t="shared" si="0"/>
-        <v>1010</v>
-      </c>
-      <c r="B12" s="2">
-        <v>100200</v>
-      </c>
-      <c r="C12" s="2">
-        <v>100210</v>
-      </c>
-      <c r="D12" s="2">
-        <v>9999</v>
-      </c>
-      <c r="E12" s="2">
-        <v>9999</v>
-      </c>
-      <c r="F12" s="2">
-        <v>9999</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="I12" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="K12" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="L12" s="2">
-        <v>0</v>
-      </c>
-      <c r="M12" s="2">
-        <v>0</v>
-      </c>
-      <c r="O12" t="b">
-        <v>0</v>
-      </c>
-      <c r="P12" s="14" t="s">
+      <c r="L12" s="15">
+        <v>0</v>
+      </c>
+      <c r="M12" s="15">
+        <v>0</v>
+      </c>
+      <c r="O12" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="P12" s="20" t="s">
         <v>88</v>
       </c>
     </row>
@@ -4598,11 +4611,11 @@
         <v>1011</v>
       </c>
       <c r="B13" s="2">
+        <v>100200</v>
+      </c>
+      <c r="C13" s="2">
         <v>100210</v>
       </c>
-      <c r="C13" s="2">
-        <v>100220</v>
-      </c>
       <c r="D13" s="2">
         <v>9999</v>
       </c>
@@ -4613,13 +4626,13 @@
         <v>9999</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>54</v>
+        <v>178</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>54</v>
+        <v>178</v>
       </c>
       <c r="J13" s="3" t="s">
         <v>37</v>
@@ -4646,11 +4659,11 @@
         <v>1012</v>
       </c>
       <c r="B14" s="2">
+        <v>100210</v>
+      </c>
+      <c r="C14" s="2">
         <v>100220</v>
       </c>
-      <c r="C14" s="2">
-        <v>100400</v>
-      </c>
       <c r="D14" s="2">
         <v>9999</v>
       </c>
@@ -4661,7 +4674,7 @@
         <v>9999</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="H14" s="6" t="s">
         <v>54</v>
@@ -4694,7 +4707,7 @@
         <v>1013</v>
       </c>
       <c r="B15" s="2">
-        <v>100300</v>
+        <v>100220</v>
       </c>
       <c r="C15" s="2">
         <v>100400</v>
@@ -4709,13 +4722,13 @@
         <v>9999</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>174</v>
+        <v>54</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>174</v>
+        <v>54</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>37</v>
@@ -4736,51 +4749,51 @@
         <v>88</v>
       </c>
     </row>
-    <row r="16" spans="1:16" s="11" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="7">
+    <row r="16" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="2">
         <f t="shared" si="0"/>
         <v>1014</v>
       </c>
-      <c r="B16" s="7">
-        <v>9999</v>
-      </c>
-      <c r="C16" s="7">
-        <v>9999</v>
-      </c>
-      <c r="D16" s="7">
-        <v>10000</v>
-      </c>
-      <c r="E16" s="7">
-        <v>9999</v>
-      </c>
-      <c r="F16" s="7">
-        <v>9999</v>
-      </c>
-      <c r="G16" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="H16" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="I16" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="J16" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="K16" s="10" t="s">
+      <c r="B16" s="2">
+        <v>100300</v>
+      </c>
+      <c r="C16" s="2">
+        <v>100400</v>
+      </c>
+      <c r="D16" s="2">
+        <v>9999</v>
+      </c>
+      <c r="E16" s="2">
+        <v>9999</v>
+      </c>
+      <c r="F16" s="2">
+        <v>9999</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="K16" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="L16" s="7">
-        <v>0</v>
-      </c>
-      <c r="M16" s="7">
-        <v>0</v>
-      </c>
-      <c r="O16" s="11" t="b">
-        <v>0</v>
-      </c>
-      <c r="P16" s="13" t="s">
+      <c r="L16" s="2">
+        <v>0</v>
+      </c>
+      <c r="M16" s="2">
+        <v>0</v>
+      </c>
+      <c r="O16" t="b">
+        <v>0</v>
+      </c>
+      <c r="P16" s="14" t="s">
         <v>88</v>
       </c>
     </row>
@@ -4796,7 +4809,7 @@
         <v>9999</v>
       </c>
       <c r="D17" s="7">
-        <v>65</v>
+        <v>10000</v>
       </c>
       <c r="E17" s="7">
         <v>9999</v>
@@ -4805,7 +4818,7 @@
         <v>9999</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>132</v>
+        <v>160</v>
       </c>
       <c r="H17" s="8" t="s">
         <v>54</v>
@@ -4814,7 +4827,7 @@
         <v>54</v>
       </c>
       <c r="J17" s="8" t="s">
-        <v>133</v>
+        <v>95</v>
       </c>
       <c r="K17" s="10" t="s">
         <v>167</v>
@@ -4844,7 +4857,7 @@
         <v>9999</v>
       </c>
       <c r="D18" s="7">
-        <v>10000</v>
+        <v>65</v>
       </c>
       <c r="E18" s="7">
         <v>9999</v>
@@ -4853,7 +4866,7 @@
         <v>9999</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="H18" s="8" t="s">
         <v>54</v>
@@ -4862,7 +4875,7 @@
         <v>54</v>
       </c>
       <c r="J18" s="8" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="K18" s="10" t="s">
         <v>167</v>
@@ -4880,51 +4893,51 @@
         <v>88</v>
       </c>
     </row>
-    <row r="19" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="2">
+    <row r="19" spans="1:16" s="11" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="7">
         <f t="shared" si="0"/>
         <v>1017</v>
       </c>
-      <c r="B19" s="2">
-        <v>100400</v>
-      </c>
-      <c r="C19" s="2">
-        <v>100410</v>
-      </c>
-      <c r="D19" s="2">
-        <v>9999</v>
-      </c>
-      <c r="E19" s="2">
-        <v>9999</v>
-      </c>
-      <c r="F19" s="2">
-        <v>9999</v>
-      </c>
-      <c r="G19" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="H19" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="I19" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="K19" s="4" t="s">
+      <c r="B19" s="7">
+        <v>9999</v>
+      </c>
+      <c r="C19" s="7">
+        <v>9999</v>
+      </c>
+      <c r="D19" s="7">
+        <v>10000</v>
+      </c>
+      <c r="E19" s="7">
+        <v>9999</v>
+      </c>
+      <c r="F19" s="7">
+        <v>9999</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="I19" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="J19" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="K19" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="L19" s="2">
-        <v>0</v>
-      </c>
-      <c r="M19" s="2">
-        <v>0</v>
-      </c>
-      <c r="O19" t="b">
-        <v>0</v>
-      </c>
-      <c r="P19" s="14" t="s">
+      <c r="L19" s="7">
+        <v>0</v>
+      </c>
+      <c r="M19" s="7">
+        <v>0</v>
+      </c>
+      <c r="O19" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="P19" s="13" t="s">
         <v>88</v>
       </c>
     </row>
@@ -4934,11 +4947,11 @@
         <v>1018</v>
       </c>
       <c r="B20" s="2">
+        <v>100400</v>
+      </c>
+      <c r="C20" s="2">
         <v>100410</v>
       </c>
-      <c r="C20" s="2">
-        <v>100420</v>
-      </c>
       <c r="D20" s="2">
         <v>9999</v>
       </c>
@@ -4949,13 +4962,13 @@
         <v>9999</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>54</v>
+        <v>168</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>54</v>
+        <v>175</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>37</v>
@@ -4982,11 +4995,11 @@
         <v>1019</v>
       </c>
       <c r="B21" s="2">
+        <v>100410</v>
+      </c>
+      <c r="C21" s="2">
         <v>100420</v>
       </c>
-      <c r="C21" s="2">
-        <v>100500</v>
-      </c>
       <c r="D21" s="2">
         <v>9999</v>
       </c>
@@ -4997,7 +5010,7 @@
         <v>9999</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>168</v>
+        <v>184</v>
       </c>
       <c r="H21" s="6" t="s">
         <v>54</v>
@@ -5030,11 +5043,11 @@
         <v>1020</v>
       </c>
       <c r="B22" s="2">
+        <v>100420</v>
+      </c>
+      <c r="C22" s="2">
         <v>100500</v>
       </c>
-      <c r="C22" s="2">
-        <v>9999</v>
-      </c>
       <c r="D22" s="2">
         <v>9999</v>
       </c>
@@ -5045,31 +5058,79 @@
         <v>9999</v>
       </c>
       <c r="G22" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="K22" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="L22" s="2">
+        <v>0</v>
+      </c>
+      <c r="M22" s="2">
+        <v>0</v>
+      </c>
+      <c r="O22" t="b">
+        <v>0</v>
+      </c>
+      <c r="P22" s="14" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="2">
+        <f t="shared" si="0"/>
+        <v>1021</v>
+      </c>
+      <c r="B23" s="2">
+        <v>100500</v>
+      </c>
+      <c r="C23" s="2">
+        <v>9999</v>
+      </c>
+      <c r="D23" s="2">
+        <v>9999</v>
+      </c>
+      <c r="E23" s="2">
+        <v>9999</v>
+      </c>
+      <c r="F23" s="2">
+        <v>9999</v>
+      </c>
+      <c r="G23" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="H22" s="6" t="s">
+      <c r="H23" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="I22" s="6" t="s">
+      <c r="I23" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="J22" s="3" t="s">
+      <c r="J23" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="K22" s="4" t="s">
+      <c r="K23" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="L22" s="2">
-        <v>0</v>
-      </c>
-      <c r="M22" s="2">
-        <v>0</v>
-      </c>
-      <c r="N22" s="5"/>
-      <c r="O22" t="b">
-        <v>0</v>
-      </c>
-      <c r="P22" s="14" t="s">
+      <c r="L23" s="2">
+        <v>0</v>
+      </c>
+      <c r="M23" s="2">
+        <v>0</v>
+      </c>
+      <c r="N23" s="5"/>
+      <c r="O23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P23" s="14" t="s">
         <v>74</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_GirlLikeSetCompoDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_GirlLikeSetCompoDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EBF711D-3D5D-4F16-B442-A3D27967F4DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F008D380-6D3F-4EFC-AB32-EB9123F51EBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2520" yWindow="660" windowWidth="25560" windowHeight="14355" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3180" yWindow="1035" windowWidth="25560" windowHeight="14355" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_Stage1_Set" sheetId="2" r:id="rId1"/>
@@ -1285,16 +1285,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>各地で、エデンのレシピを集めよう！</t>
-    <rPh sb="0" eb="2">
-      <t>カクチ</t>
-    </rPh>
-    <rPh sb="12" eb="13">
-      <t>アツ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>女王様に会いにいこう！</t>
     <rPh sb="0" eb="3">
       <t>ジョオウサマ</t>
@@ -1315,16 +1305,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>3番目のレシピを集めよう！</t>
-    <rPh sb="1" eb="3">
-      <t>バンメ</t>
-    </rPh>
-    <rPh sb="8" eb="9">
-      <t>アツ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>白クジラさんに会いにいこう！</t>
     <rPh sb="0" eb="1">
       <t>シロ</t>
@@ -1351,6 +1331,23 @@
     <t>プラトンアカデミーコンテストで優勝しよう！</t>
     <rPh sb="15" eb="17">
       <t>ユウショウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>「アルク・アン・シェル」で優勝しよう！</t>
+    <rPh sb="13" eb="15">
+      <t>ユウショウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>コンテストに出て、エデンのレシピを集めよう！</t>
+    <rPh sb="6" eb="7">
+      <t>デ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>アツ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -4434,7 +4431,7 @@
         <v>9999</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H9" s="6" t="s">
         <v>54</v>
@@ -4482,7 +4479,7 @@
         <v>9999</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>54</v>
@@ -4530,7 +4527,7 @@
         <v>9999</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>54</v>
@@ -4674,7 +4671,7 @@
         <v>9999</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="H14" s="6" t="s">
         <v>54</v>
@@ -4722,7 +4719,7 @@
         <v>9999</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="H15" s="6" t="s">
         <v>54</v>
@@ -4962,7 +4959,7 @@
         <v>9999</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H20" s="6" t="s">
         <v>168</v>
@@ -5010,7 +5007,7 @@
         <v>9999</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H21" s="6" t="s">
         <v>54</v>

--- a/Assets/Resources/Excel/Entity_GirlLikeSetCompoDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_GirlLikeSetCompoDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F008D380-6D3F-4EFC-AB32-EB9123F51EBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CEBA172-34E6-454C-B4DE-47DBD752D494}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3180" yWindow="1035" windowWidth="25560" windowHeight="14355" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2865" yWindow="1020" windowWidth="25560" windowHeight="14355" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_Stage1_Set" sheetId="2" r:id="rId1"/>
@@ -1120,13 +1120,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>コンテストに出場しよう！</t>
-    <rPh sb="6" eb="8">
-      <t>シュツジョウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>ヒカリにお菓子を覚えてもらう！</t>
     <rPh sb="5" eb="7">
       <t>カシ</t>
@@ -1348,6 +1341,16 @@
     </rPh>
     <rPh sb="17" eb="18">
       <t>アツ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>初！コンテストに出場しよう！</t>
+    <rPh sb="0" eb="1">
+      <t>ハツ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>シュツジョウ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -4095,10 +4098,10 @@
         <v>42</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>37</v>
@@ -4164,7 +4167,7 @@
         <v>0</v>
       </c>
       <c r="P3" s="14" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -4188,16 +4191,16 @@
         <v>12</v>
       </c>
       <c r="G4" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="J4" s="6" t="s">
         <v>162</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="J4" s="6" t="s">
-        <v>163</v>
       </c>
       <c r="K4" s="4" t="s">
         <v>11</v>
@@ -4215,7 +4218,7 @@
         <v>0</v>
       </c>
       <c r="P4" s="14" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -4239,7 +4242,7 @@
         <v>9999</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H5" s="6" t="s">
         <v>54</v>
@@ -4251,7 +4254,7 @@
         <v>140</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="L5" s="2">
         <v>0</v>
@@ -4299,7 +4302,7 @@
         <v>37</v>
       </c>
       <c r="K6" s="18" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L6" s="15">
         <v>0</v>
@@ -4335,19 +4338,19 @@
         <v>9999</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>159</v>
+        <v>186</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>37</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L7" s="2">
         <v>0</v>
@@ -4383,7 +4386,7 @@
         <v>9999</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H8" s="6" t="s">
         <v>54</v>
@@ -4395,7 +4398,7 @@
         <v>37</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L8" s="2">
         <v>0</v>
@@ -4431,7 +4434,7 @@
         <v>9999</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H9" s="6" t="s">
         <v>54</v>
@@ -4440,10 +4443,10 @@
         <v>54</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L9" s="2">
         <v>0</v>
@@ -4479,7 +4482,7 @@
         <v>9999</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>54</v>
@@ -4491,7 +4494,7 @@
         <v>37</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L10" s="2">
         <v>0</v>
@@ -4527,7 +4530,7 @@
         <v>9999</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>54</v>
@@ -4539,7 +4542,7 @@
         <v>37</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L11" s="2">
         <v>0</v>
@@ -4575,7 +4578,7 @@
         <v>9999</v>
       </c>
       <c r="G12" s="16" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H12" s="16" t="s">
         <v>54</v>
@@ -4587,7 +4590,7 @@
         <v>37</v>
       </c>
       <c r="K12" s="18" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L12" s="15">
         <v>0</v>
@@ -4623,19 +4626,19 @@
         <v>9999</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J13" s="3" t="s">
         <v>37</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L13" s="2">
         <v>0</v>
@@ -4671,7 +4674,7 @@
         <v>9999</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H14" s="6" t="s">
         <v>54</v>
@@ -4683,7 +4686,7 @@
         <v>37</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L14" s="2">
         <v>0</v>
@@ -4719,7 +4722,7 @@
         <v>9999</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H15" s="6" t="s">
         <v>54</v>
@@ -4731,7 +4734,7 @@
         <v>37</v>
       </c>
       <c r="K15" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L15" s="2">
         <v>0</v>
@@ -4767,19 +4770,19 @@
         <v>9999</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>37</v>
       </c>
       <c r="K16" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L16" s="2">
         <v>0</v>
@@ -4815,7 +4818,7 @@
         <v>9999</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H17" s="8" t="s">
         <v>54</v>
@@ -4827,7 +4830,7 @@
         <v>95</v>
       </c>
       <c r="K17" s="10" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L17" s="7">
         <v>0</v>
@@ -4875,7 +4878,7 @@
         <v>133</v>
       </c>
       <c r="K18" s="10" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L18" s="7">
         <v>0</v>
@@ -4923,7 +4926,7 @@
         <v>145</v>
       </c>
       <c r="K19" s="10" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L19" s="7">
         <v>0</v>
@@ -4959,19 +4962,19 @@
         <v>9999</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>37</v>
       </c>
       <c r="K20" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L20" s="2">
         <v>0</v>
@@ -5007,7 +5010,7 @@
         <v>9999</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H21" s="6" t="s">
         <v>54</v>
@@ -5019,7 +5022,7 @@
         <v>37</v>
       </c>
       <c r="K21" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L21" s="2">
         <v>0</v>
@@ -5055,7 +5058,7 @@
         <v>9999</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H22" s="6" t="s">
         <v>54</v>
@@ -5067,7 +5070,7 @@
         <v>37</v>
       </c>
       <c r="K22" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L22" s="2">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_GirlLikeSetCompoDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_GirlLikeSetCompoDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CEBA172-34E6-454C-B4DE-47DBD752D494}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{292E49F2-B5A5-4FF3-9663-0846425C7E97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2865" yWindow="1020" windowWidth="25560" windowHeight="14355" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1125" yWindow="1125" windowWidth="25560" windowHeight="14370" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_Stage1_Set" sheetId="2" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="188">
   <si>
     <t>desc</t>
   </si>
@@ -1351,6 +1351,16 @@
     </rPh>
     <rPh sb="8" eb="10">
       <t>シュツジョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>☆スターを5個集めよう！</t>
+    <rPh sb="6" eb="7">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>アツ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -4014,7 +4024,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0D5A12D-B9F6-41BC-8E5B-D7E79CC788E5}">
-  <dimension ref="A1:P23"/>
+  <dimension ref="A1:P24"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="7" max="7" width="17.28515625" customWidth="1"/>
@@ -4124,7 +4134,7 @@
     </row>
     <row r="3" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
-        <f t="shared" ref="A3:A23" si="0">ROW()-2+1000</f>
+        <f t="shared" ref="A3:A24" si="0">ROW()-2+1000</f>
         <v>1001</v>
       </c>
       <c r="B3" s="2">
@@ -4518,7 +4528,7 @@
         <v>100140</v>
       </c>
       <c r="C11" s="2">
-        <v>100200</v>
+        <v>100150</v>
       </c>
       <c r="D11" s="2">
         <v>9999</v>
@@ -4530,7 +4540,7 @@
         <v>9999</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>54</v>
@@ -4557,99 +4567,99 @@
         <v>88</v>
       </c>
     </row>
-    <row r="12" spans="1:16" s="19" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="15">
+    <row r="12" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="2">
         <f t="shared" si="0"/>
         <v>1010</v>
       </c>
-      <c r="B12" s="7">
-        <v>9999</v>
-      </c>
-      <c r="C12" s="7">
-        <v>9999</v>
-      </c>
-      <c r="D12" s="15">
-        <v>9999</v>
-      </c>
-      <c r="E12" s="15">
-        <v>9999</v>
-      </c>
-      <c r="F12" s="15">
-        <v>9999</v>
-      </c>
-      <c r="G12" s="16" t="s">
+      <c r="B12" s="2">
+        <v>100150</v>
+      </c>
+      <c r="C12" s="2">
+        <v>100200</v>
+      </c>
+      <c r="D12" s="2">
+        <v>9999</v>
+      </c>
+      <c r="E12" s="2">
+        <v>9999</v>
+      </c>
+      <c r="F12" s="2">
+        <v>9999</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="L12" s="2">
+        <v>0</v>
+      </c>
+      <c r="M12" s="2">
+        <v>0</v>
+      </c>
+      <c r="O12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P12" s="14" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" s="19" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="15">
+        <f t="shared" si="0"/>
+        <v>1011</v>
+      </c>
+      <c r="B13" s="7">
+        <v>9999</v>
+      </c>
+      <c r="C13" s="7">
+        <v>9999</v>
+      </c>
+      <c r="D13" s="15">
+        <v>9999</v>
+      </c>
+      <c r="E13" s="15">
+        <v>9999</v>
+      </c>
+      <c r="F13" s="15">
+        <v>9999</v>
+      </c>
+      <c r="G13" s="16" t="s">
         <v>169</v>
       </c>
-      <c r="H12" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="I12" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="J12" s="17" t="s">
+      <c r="H13" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="I13" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="J13" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="K12" s="18" t="s">
+      <c r="K13" s="18" t="s">
         <v>166</v>
       </c>
-      <c r="L12" s="15">
-        <v>0</v>
-      </c>
-      <c r="M12" s="15">
-        <v>0</v>
-      </c>
-      <c r="O12" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="P12" s="20" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="2">
-        <f t="shared" si="0"/>
-        <v>1011</v>
-      </c>
-      <c r="B13" s="2">
-        <v>100200</v>
-      </c>
-      <c r="C13" s="2">
-        <v>100210</v>
-      </c>
-      <c r="D13" s="2">
-        <v>9999</v>
-      </c>
-      <c r="E13" s="2">
-        <v>9999</v>
-      </c>
-      <c r="F13" s="2">
-        <v>9999</v>
-      </c>
-      <c r="G13" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="H13" s="6" t="s">
-        <v>177</v>
-      </c>
-      <c r="I13" s="6" t="s">
-        <v>177</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="K13" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="L13" s="2">
-        <v>0</v>
-      </c>
-      <c r="M13" s="2">
-        <v>0</v>
-      </c>
-      <c r="O13" t="b">
-        <v>0</v>
-      </c>
-      <c r="P13" s="14" t="s">
+      <c r="L13" s="15">
+        <v>0</v>
+      </c>
+      <c r="M13" s="15">
+        <v>0</v>
+      </c>
+      <c r="O13" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="P13" s="20" t="s">
         <v>88</v>
       </c>
     </row>
@@ -4659,11 +4669,11 @@
         <v>1012</v>
       </c>
       <c r="B14" s="2">
+        <v>100200</v>
+      </c>
+      <c r="C14" s="2">
         <v>100210</v>
       </c>
-      <c r="C14" s="2">
-        <v>100220</v>
-      </c>
       <c r="D14" s="2">
         <v>9999</v>
       </c>
@@ -4674,13 +4684,13 @@
         <v>9999</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>185</v>
+        <v>172</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>54</v>
+        <v>177</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>54</v>
+        <v>177</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>37</v>
@@ -4707,11 +4717,11 @@
         <v>1013</v>
       </c>
       <c r="B15" s="2">
+        <v>100210</v>
+      </c>
+      <c r="C15" s="2">
         <v>100220</v>
       </c>
-      <c r="C15" s="2">
-        <v>100400</v>
-      </c>
       <c r="D15" s="2">
         <v>9999</v>
       </c>
@@ -4722,7 +4732,7 @@
         <v>9999</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H15" s="6" t="s">
         <v>54</v>
@@ -4755,7 +4765,7 @@
         <v>1014</v>
       </c>
       <c r="B16" s="2">
-        <v>100300</v>
+        <v>100220</v>
       </c>
       <c r="C16" s="2">
         <v>100400</v>
@@ -4770,13 +4780,13 @@
         <v>9999</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>173</v>
+        <v>54</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>173</v>
+        <v>54</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>37</v>
@@ -4797,51 +4807,51 @@
         <v>88</v>
       </c>
     </row>
-    <row r="17" spans="1:16" s="11" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="7">
+    <row r="17" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="2">
         <f t="shared" si="0"/>
         <v>1015</v>
       </c>
-      <c r="B17" s="7">
-        <v>9999</v>
-      </c>
-      <c r="C17" s="7">
-        <v>9999</v>
-      </c>
-      <c r="D17" s="7">
-        <v>10000</v>
-      </c>
-      <c r="E17" s="7">
-        <v>9999</v>
-      </c>
-      <c r="F17" s="7">
-        <v>9999</v>
-      </c>
-      <c r="G17" s="8" t="s">
-        <v>159</v>
-      </c>
-      <c r="H17" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="I17" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="J17" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="K17" s="10" t="s">
+      <c r="B17" s="2">
+        <v>100300</v>
+      </c>
+      <c r="C17" s="2">
+        <v>100400</v>
+      </c>
+      <c r="D17" s="2">
+        <v>9999</v>
+      </c>
+      <c r="E17" s="2">
+        <v>9999</v>
+      </c>
+      <c r="F17" s="2">
+        <v>9999</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="K17" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="L17" s="7">
-        <v>0</v>
-      </c>
-      <c r="M17" s="7">
-        <v>0</v>
-      </c>
-      <c r="O17" s="11" t="b">
-        <v>0</v>
-      </c>
-      <c r="P17" s="13" t="s">
+      <c r="L17" s="2">
+        <v>0</v>
+      </c>
+      <c r="M17" s="2">
+        <v>0</v>
+      </c>
+      <c r="O17" t="b">
+        <v>0</v>
+      </c>
+      <c r="P17" s="14" t="s">
         <v>88</v>
       </c>
     </row>
@@ -4857,7 +4867,7 @@
         <v>9999</v>
       </c>
       <c r="D18" s="7">
-        <v>65</v>
+        <v>10000</v>
       </c>
       <c r="E18" s="7">
         <v>9999</v>
@@ -4866,7 +4876,7 @@
         <v>9999</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>132</v>
+        <v>159</v>
       </c>
       <c r="H18" s="8" t="s">
         <v>54</v>
@@ -4875,7 +4885,7 @@
         <v>54</v>
       </c>
       <c r="J18" s="8" t="s">
-        <v>133</v>
+        <v>95</v>
       </c>
       <c r="K18" s="10" t="s">
         <v>166</v>
@@ -4905,7 +4915,7 @@
         <v>9999</v>
       </c>
       <c r="D19" s="7">
-        <v>10000</v>
+        <v>65</v>
       </c>
       <c r="E19" s="7">
         <v>9999</v>
@@ -4914,7 +4924,7 @@
         <v>9999</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="H19" s="8" t="s">
         <v>54</v>
@@ -4923,7 +4933,7 @@
         <v>54</v>
       </c>
       <c r="J19" s="8" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="K19" s="10" t="s">
         <v>166</v>
@@ -4941,51 +4951,51 @@
         <v>88</v>
       </c>
     </row>
-    <row r="20" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="2">
+    <row r="20" spans="1:16" s="11" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="7">
         <f t="shared" si="0"/>
         <v>1018</v>
       </c>
-      <c r="B20" s="2">
-        <v>100400</v>
-      </c>
-      <c r="C20" s="2">
-        <v>100410</v>
-      </c>
-      <c r="D20" s="2">
-        <v>9999</v>
-      </c>
-      <c r="E20" s="2">
-        <v>9999</v>
-      </c>
-      <c r="F20" s="2">
-        <v>9999</v>
-      </c>
-      <c r="G20" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="I20" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="K20" s="4" t="s">
+      <c r="B20" s="7">
+        <v>9999</v>
+      </c>
+      <c r="C20" s="7">
+        <v>9999</v>
+      </c>
+      <c r="D20" s="7">
+        <v>10000</v>
+      </c>
+      <c r="E20" s="7">
+        <v>9999</v>
+      </c>
+      <c r="F20" s="7">
+        <v>9999</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="I20" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="J20" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="K20" s="10" t="s">
         <v>166</v>
       </c>
-      <c r="L20" s="2">
-        <v>0</v>
-      </c>
-      <c r="M20" s="2">
-        <v>0</v>
-      </c>
-      <c r="O20" t="b">
-        <v>0</v>
-      </c>
-      <c r="P20" s="14" t="s">
+      <c r="L20" s="7">
+        <v>0</v>
+      </c>
+      <c r="M20" s="7">
+        <v>0</v>
+      </c>
+      <c r="O20" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="P20" s="13" t="s">
         <v>88</v>
       </c>
     </row>
@@ -4995,11 +5005,11 @@
         <v>1019</v>
       </c>
       <c r="B21" s="2">
+        <v>100400</v>
+      </c>
+      <c r="C21" s="2">
         <v>100410</v>
       </c>
-      <c r="C21" s="2">
-        <v>100420</v>
-      </c>
       <c r="D21" s="2">
         <v>9999</v>
       </c>
@@ -5010,13 +5020,13 @@
         <v>9999</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>54</v>
+        <v>167</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>54</v>
+        <v>174</v>
       </c>
       <c r="J21" s="3" t="s">
         <v>37</v>
@@ -5043,11 +5053,11 @@
         <v>1020</v>
       </c>
       <c r="B22" s="2">
+        <v>100410</v>
+      </c>
+      <c r="C22" s="2">
         <v>100420</v>
       </c>
-      <c r="C22" s="2">
-        <v>100500</v>
-      </c>
       <c r="D22" s="2">
         <v>9999</v>
       </c>
@@ -5058,7 +5068,7 @@
         <v>9999</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="H22" s="6" t="s">
         <v>54</v>
@@ -5091,11 +5101,11 @@
         <v>1021</v>
       </c>
       <c r="B23" s="2">
+        <v>100420</v>
+      </c>
+      <c r="C23" s="2">
         <v>100500</v>
       </c>
-      <c r="C23" s="2">
-        <v>9999</v>
-      </c>
       <c r="D23" s="2">
         <v>9999</v>
       </c>
@@ -5106,31 +5116,79 @@
         <v>9999</v>
       </c>
       <c r="G23" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="H23" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="I23" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="K23" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="L23" s="2">
+        <v>0</v>
+      </c>
+      <c r="M23" s="2">
+        <v>0</v>
+      </c>
+      <c r="O23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P23" s="14" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="2">
+        <f t="shared" si="0"/>
+        <v>1022</v>
+      </c>
+      <c r="B24" s="2">
+        <v>100500</v>
+      </c>
+      <c r="C24" s="2">
+        <v>9999</v>
+      </c>
+      <c r="D24" s="2">
+        <v>9999</v>
+      </c>
+      <c r="E24" s="2">
+        <v>9999</v>
+      </c>
+      <c r="F24" s="2">
+        <v>9999</v>
+      </c>
+      <c r="G24" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="H23" s="6" t="s">
+      <c r="H24" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="I23" s="6" t="s">
+      <c r="I24" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="J23" s="3" t="s">
+      <c r="J24" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="K23" s="4" t="s">
+      <c r="K24" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="L23" s="2">
-        <v>0</v>
-      </c>
-      <c r="M23" s="2">
-        <v>0</v>
-      </c>
-      <c r="N23" s="5"/>
-      <c r="O23" t="b">
-        <v>0</v>
-      </c>
-      <c r="P23" s="14" t="s">
+      <c r="L24" s="2">
+        <v>0</v>
+      </c>
+      <c r="M24" s="2">
+        <v>0</v>
+      </c>
+      <c r="N24" s="5"/>
+      <c r="O24" t="b">
+        <v>0</v>
+      </c>
+      <c r="P24" s="14" t="s">
         <v>74</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_GirlLikeSetCompoDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_GirlLikeSetCompoDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{292E49F2-B5A5-4FF3-9663-0846425C7E97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57C5785D-D22C-47C9-9E45-43732D799098}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1125" yWindow="1125" windowWidth="25560" windowHeight="14370" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1905" yWindow="825" windowWidth="25485" windowHeight="14370" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_Stage1_Set" sheetId="2" r:id="rId1"/>
@@ -1355,11 +1355,11 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>☆スターを5個集めよう！</t>
-    <rPh sb="6" eb="7">
+    <t>コンテストで☆スターを5個集めよう！</t>
+    <rPh sb="12" eb="13">
       <t>コ</t>
     </rPh>
-    <rPh sb="7" eb="8">
+    <rPh sb="13" eb="14">
       <t>アツ</t>
     </rPh>
     <phoneticPr fontId="2"/>

--- a/Assets/Resources/Excel/Entity_GirlLikeSetCompoDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_GirlLikeSetCompoDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57C5785D-D22C-47C9-9E45-43732D799098}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F26BFBD-F7C3-4FD3-968F-0CA505DF8EC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1905" yWindow="825" windowWidth="25485" windowHeight="14370" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3315" yWindow="1830" windowWidth="25485" windowHeight="14370" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_Stage1_Set" sheetId="2" r:id="rId1"/>
@@ -1217,16 +1217,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>お城へ行ってみよう！</t>
-    <rPh sb="1" eb="2">
-      <t>シロ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>イ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>秋コンテストで優勝しよう！</t>
     <rPh sb="0" eb="1">
       <t>アキ</t>
@@ -1361,6 +1351,16 @@
     </rPh>
     <rPh sb="13" eb="14">
       <t>アツ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>オランジーナ城へ行ってみよう！</t>
+    <rPh sb="6" eb="7">
+      <t>シロ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>イ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -4111,7 +4111,7 @@
         <v>170</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>37</v>
@@ -4348,13 +4348,13 @@
         <v>9999</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H7" s="6" t="s">
         <v>171</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>37</v>
@@ -4444,7 +4444,7 @@
         <v>9999</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H9" s="6" t="s">
         <v>54</v>
@@ -4453,7 +4453,7 @@
         <v>54</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K9" s="4" t="s">
         <v>166</v>
@@ -4492,7 +4492,7 @@
         <v>9999</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>54</v>
@@ -4540,7 +4540,7 @@
         <v>9999</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>54</v>
@@ -4588,7 +4588,7 @@
         <v>9999</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>54</v>
@@ -4684,13 +4684,13 @@
         <v>9999</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>37</v>
@@ -4732,7 +4732,7 @@
         <v>9999</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H15" s="6" t="s">
         <v>54</v>
@@ -4780,7 +4780,7 @@
         <v>9999</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H16" s="6" t="s">
         <v>54</v>
@@ -4828,13 +4828,13 @@
         <v>9999</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J17" s="3" t="s">
         <v>37</v>
@@ -5020,13 +5020,13 @@
         <v>9999</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H21" s="6" t="s">
         <v>167</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J21" s="3" t="s">
         <v>37</v>
@@ -5068,7 +5068,7 @@
         <v>9999</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H22" s="6" t="s">
         <v>54</v>

--- a/Assets/Resources/Excel/Entity_GirlLikeSetCompoDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_GirlLikeSetCompoDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F26BFBD-F7C3-4FD3-968F-0CA505DF8EC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D335411-2A6A-4814-B7B1-A3B2845298E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3315" yWindow="1830" windowWidth="25485" windowHeight="14370" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="25485" windowHeight="14370" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_Stage1_Set" sheetId="2" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="187">
   <si>
     <t>desc</t>
   </si>
@@ -1264,16 +1264,6 @@
     <t>まほうのお菓子</t>
     <rPh sb="5" eb="7">
       <t>カシ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>女王様に会いにいこう！</t>
-    <rPh sb="0" eb="3">
-      <t>ジョオウサマ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>ア</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -4348,7 +4338,7 @@
         <v>9999</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H7" s="6" t="s">
         <v>171</v>
@@ -4444,7 +4434,7 @@
         <v>9999</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H9" s="6" t="s">
         <v>54</v>
@@ -4492,7 +4482,7 @@
         <v>9999</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>54</v>
@@ -4540,7 +4530,7 @@
         <v>9999</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>54</v>
@@ -4588,7 +4578,7 @@
         <v>9999</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>54</v>
@@ -4684,7 +4674,7 @@
         <v>9999</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H14" s="6" t="s">
         <v>176</v>
@@ -4732,7 +4722,7 @@
         <v>9999</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H15" s="6" t="s">
         <v>54</v>
@@ -4780,7 +4770,7 @@
         <v>9999</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H16" s="6" t="s">
         <v>54</v>
@@ -5008,7 +4998,7 @@
         <v>100400</v>
       </c>
       <c r="C21" s="2">
-        <v>100410</v>
+        <v>100420</v>
       </c>
       <c r="D21" s="2">
         <v>9999</v>
@@ -5020,7 +5010,7 @@
         <v>9999</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H21" s="6" t="s">
         <v>167</v>
@@ -5047,51 +5037,51 @@
         <v>88</v>
       </c>
     </row>
-    <row r="22" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="2">
+    <row r="22" spans="1:16" s="19" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="15">
         <f t="shared" si="0"/>
         <v>1020</v>
       </c>
-      <c r="B22" s="2">
+      <c r="B22" s="15">
         <v>100410</v>
       </c>
-      <c r="C22" s="2">
+      <c r="C22" s="15">
         <v>100420</v>
       </c>
-      <c r="D22" s="2">
-        <v>9999</v>
-      </c>
-      <c r="E22" s="2">
-        <v>9999</v>
-      </c>
-      <c r="F22" s="2">
-        <v>9999</v>
-      </c>
-      <c r="G22" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="I22" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="J22" s="3" t="s">
+      <c r="D22" s="15">
+        <v>9999</v>
+      </c>
+      <c r="E22" s="15">
+        <v>9999</v>
+      </c>
+      <c r="F22" s="15">
+        <v>9999</v>
+      </c>
+      <c r="G22" s="16" t="s">
+        <v>179</v>
+      </c>
+      <c r="H22" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="I22" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="J22" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="K22" s="4" t="s">
+      <c r="K22" s="18" t="s">
         <v>166</v>
       </c>
-      <c r="L22" s="2">
-        <v>0</v>
-      </c>
-      <c r="M22" s="2">
-        <v>0</v>
-      </c>
-      <c r="O22" t="b">
-        <v>0</v>
-      </c>
-      <c r="P22" s="14" t="s">
+      <c r="L22" s="15">
+        <v>0</v>
+      </c>
+      <c r="M22" s="15">
+        <v>0</v>
+      </c>
+      <c r="O22" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="P22" s="20" t="s">
         <v>88</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_GirlLikeSetCompoDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_GirlLikeSetCompoDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D335411-2A6A-4814-B7B1-A3B2845298E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0959D3A0-173C-45F7-92CC-9A5A5C4ADFA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="25485" windowHeight="14370" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1935" yWindow="1005" windowWidth="25485" windowHeight="14370" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_Stage1_Set" sheetId="2" r:id="rId1"/>
@@ -1315,16 +1315,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>コンテストに出て、エデンのレシピを集めよう！</t>
-    <rPh sb="6" eb="7">
-      <t>デ</t>
-    </rPh>
-    <rPh sb="17" eb="18">
-      <t>アツ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>初！コンテストに出場しよう！</t>
     <rPh sb="0" eb="1">
       <t>ハツ</t>
@@ -1351,6 +1341,13 @@
     </rPh>
     <rPh sb="8" eb="9">
       <t>イ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>エデンのレシピを集めよう！</t>
+    <rPh sb="8" eb="9">
+      <t>アツ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -4338,7 +4335,7 @@
         <v>9999</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H7" s="6" t="s">
         <v>171</v>
@@ -4470,7 +4467,7 @@
         <v>100130</v>
       </c>
       <c r="C10" s="2">
-        <v>100140</v>
+        <v>100150</v>
       </c>
       <c r="D10" s="2">
         <v>9999</v>
@@ -4530,7 +4527,7 @@
         <v>9999</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>54</v>
@@ -4674,7 +4671,7 @@
         <v>9999</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H14" s="6" t="s">
         <v>176</v>
@@ -4722,7 +4719,7 @@
         <v>9999</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="H15" s="6" t="s">
         <v>54</v>

--- a/Assets/Resources/Excel/Entity_GirlLikeSetCompoDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_GirlLikeSetCompoDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0959D3A0-173C-45F7-92CC-9A5A5C4ADFA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F43F3D7A-3B7F-4105-AE45-C3B0921E5131}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1935" yWindow="1005" windowWidth="25485" windowHeight="14370" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="25485" windowHeight="14370" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_Stage1_Set" sheetId="2" r:id="rId1"/>
@@ -1210,13 +1210,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>初のコンテスト！</t>
-    <rPh sb="0" eb="1">
-      <t>ハツ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>秋コンテストで優勝しよう！</t>
     <rPh sb="0" eb="1">
       <t>アキ</t>
@@ -1234,13 +1227,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>初のコンテスト！！</t>
-    <rPh sb="0" eb="1">
-      <t>ハツ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>ようこそ！オランジーナの街へ！！</t>
     <rPh sb="12" eb="13">
       <t>マチ</t>
@@ -1348,6 +1334,20 @@
     <t>エデンのレシピを集めよう！</t>
     <rPh sb="8" eb="9">
       <t>アツ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>春のコンテスト！</t>
+    <rPh sb="0" eb="1">
+      <t>ハル</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>春のコンテスト！！</t>
+    <rPh sb="0" eb="1">
+      <t>ハル</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -4098,7 +4098,7 @@
         <v>170</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>37</v>
@@ -4335,13 +4335,13 @@
         <v>9999</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>37</v>
@@ -4431,7 +4431,7 @@
         <v>9999</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H9" s="6" t="s">
         <v>54</v>
@@ -4440,7 +4440,7 @@
         <v>54</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="K9" s="4" t="s">
         <v>166</v>
@@ -4479,7 +4479,7 @@
         <v>9999</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>54</v>
@@ -4527,7 +4527,7 @@
         <v>9999</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>54</v>
@@ -4575,7 +4575,7 @@
         <v>9999</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>54</v>
@@ -4671,13 +4671,13 @@
         <v>9999</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>37</v>
@@ -4719,7 +4719,7 @@
         <v>9999</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H15" s="6" t="s">
         <v>54</v>
@@ -4767,7 +4767,7 @@
         <v>9999</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H16" s="6" t="s">
         <v>54</v>
@@ -4815,13 +4815,13 @@
         <v>9999</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J17" s="3" t="s">
         <v>37</v>
@@ -5007,13 +5007,13 @@
         <v>9999</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="H21" s="6" t="s">
         <v>167</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J21" s="3" t="s">
         <v>37</v>
@@ -5055,7 +5055,7 @@
         <v>9999</v>
       </c>
       <c r="G22" s="16" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="H22" s="16" t="s">
         <v>54</v>

--- a/Assets/Resources/Excel/Entity_GirlLikeSetCompoDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_GirlLikeSetCompoDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F43F3D7A-3B7F-4105-AE45-C3B0921E5131}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44E973FA-AC6F-49B3-9671-1FEE7A83DD3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="25485" windowHeight="14370" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="25005" windowHeight="14370" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_Stage1_Set" sheetId="2" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="186">
   <si>
     <t>desc</t>
   </si>
@@ -1234,19 +1234,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>願いを叶えるお菓子！？</t>
-    <rPh sb="0" eb="1">
-      <t>ネガ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>カナ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>カシ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>まほうのお菓子</t>
     <rPh sb="5" eb="7">
       <t>カシ</t>
@@ -1338,16 +1325,25 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>春のコンテスト！</t>
+    <t>願いを叶えるお菓子</t>
     <rPh sb="0" eb="1">
-      <t>ハル</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>春のコンテスト！！</t>
-    <rPh sb="0" eb="1">
-      <t>ハル</t>
+      <t>ネガ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>カナ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>カシ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>完璧な天才</t>
+    <rPh sb="0" eb="2">
+      <t>カンペキ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>テンサイ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -4335,13 +4331,13 @@
         <v>9999</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H7" s="6" t="s">
         <v>185</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>37</v>
@@ -4431,7 +4427,7 @@
         <v>9999</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H9" s="6" t="s">
         <v>54</v>
@@ -4440,7 +4436,7 @@
         <v>54</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K9" s="4" t="s">
         <v>166</v>
@@ -4479,7 +4475,7 @@
         <v>9999</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>54</v>
@@ -4527,7 +4523,7 @@
         <v>9999</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>54</v>
@@ -4575,7 +4571,7 @@
         <v>9999</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>54</v>
@@ -4671,13 +4667,13 @@
         <v>9999</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>37</v>
@@ -4719,7 +4715,7 @@
         <v>9999</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H15" s="6" t="s">
         <v>54</v>
@@ -4767,7 +4763,7 @@
         <v>9999</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H16" s="6" t="s">
         <v>54</v>
@@ -5007,7 +5003,7 @@
         <v>9999</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H21" s="6" t="s">
         <v>167</v>
@@ -5055,7 +5051,7 @@
         <v>9999</v>
       </c>
       <c r="G22" s="16" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H22" s="16" t="s">
         <v>54</v>

--- a/Assets/Resources/Excel/Entity_GirlLikeSetCompoDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_GirlLikeSetCompoDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44E973FA-AC6F-49B3-9671-1FEE7A83DD3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{043BE9D3-3810-4788-9105-5CB52C0921AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="25005" windowHeight="14370" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="25005" windowHeight="14370" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_Stage1_Set" sheetId="2" r:id="rId1"/>
@@ -1338,12 +1338,12 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>完璧な天才</t>
-    <rPh sb="0" eb="2">
-      <t>カンペキ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>テンサイ</t>
+    <t>春コンテストで優勝しよう！</t>
+    <rPh sb="0" eb="1">
+      <t>ハル</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ユウショウ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>

--- a/Assets/Resources/Excel/Entity_GirlLikeSetCompoDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_GirlLikeSetCompoDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{043BE9D3-3810-4788-9105-5CB52C0921AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31DB8306-255F-4D6E-8DEC-CEB036FAAF54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="25005" windowHeight="14370" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1920" yWindow="930" windowWidth="25005" windowHeight="14370" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_Stage1_Set" sheetId="2" r:id="rId1"/>
@@ -1281,13 +1281,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>「アルク・アン・シェル」で優勝しよう！</t>
-    <rPh sb="13" eb="15">
-      <t>ユウショウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>初！コンテストに出場しよう！</t>
     <rPh sb="0" eb="1">
       <t>ハツ</t>
@@ -1344,6 +1337,16 @@
     </rPh>
     <rPh sb="7" eb="9">
       <t>ユウショウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>3枚目のレシピを見つけよう！</t>
+    <rPh sb="1" eb="3">
+      <t>マイメ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ミ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -4331,13 +4334,13 @@
         <v>9999</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>37</v>
@@ -4523,7 +4526,7 @@
         <v>9999</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>54</v>
@@ -4667,13 +4670,13 @@
         <v>9999</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>37</v>
@@ -4715,7 +4718,7 @@
         <v>9999</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H15" s="6" t="s">
         <v>54</v>
@@ -4763,7 +4766,7 @@
         <v>9999</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="H16" s="6" t="s">
         <v>54</v>

--- a/Assets/Resources/Excel/Entity_GirlLikeSetCompoDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_GirlLikeSetCompoDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31DB8306-255F-4D6E-8DEC-CEB036FAAF54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA80AA7F-0C2B-4CF8-976F-024DB92AE573}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1920" yWindow="930" windowWidth="25005" windowHeight="14370" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2235" yWindow="990" windowWidth="25005" windowHeight="14355" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_Stage1_Set" sheetId="2" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="187">
   <si>
     <t>desc</t>
   </si>
@@ -1173,29 +1173,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>エデンを作ろう！</t>
-    <rPh sb="4" eb="5">
-      <t>ツク</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>春の露店通りへ行ってみよう！</t>
-    <rPh sb="0" eb="1">
-      <t>ハル</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ロテン</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>ドオ</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>イ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>コンテストで優勝しよう！</t>
     <rPh sb="6" eb="8">
       <t>ユウショウ</t>
@@ -1274,13 +1251,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>プラトンアカデミーコンテストで優勝しよう！</t>
-    <rPh sb="15" eb="17">
-      <t>ユウショウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>初！コンテストに出場しよう！</t>
     <rPh sb="0" eb="1">
       <t>ハツ</t>
@@ -1311,13 +1281,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>エデンのレシピを集めよう！</t>
-    <rPh sb="8" eb="9">
-      <t>アツ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>願いを叶えるお菓子</t>
     <rPh sb="0" eb="1">
       <t>ネガ</t>
@@ -1341,12 +1304,50 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>3枚目のレシピを見つけよう！</t>
+    <t>ソーダアイランドへ遊びに行こう！</t>
+    <rPh sb="9" eb="10">
+      <t>アソ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>イ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>3枚目のエデンのレシピ</t>
     <rPh sb="1" eb="3">
       <t>マイメ</t>
     </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>エデン作り</t>
+    <rPh sb="3" eb="4">
+      <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>エデンのレシピを追って</t>
     <rPh sb="8" eb="9">
-      <t>ミ</t>
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>レシピの噂とコンテスト</t>
+    <rPh sb="4" eb="5">
+      <t>ウワサ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>おいしい匂いの正体？</t>
+    <rPh sb="4" eb="5">
+      <t>ニオ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ショウタイ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -4010,7 +4011,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0D5A12D-B9F6-41BC-8E5B-D7E79CC788E5}">
-  <dimension ref="A1:P24"/>
+  <dimension ref="A1:P25"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="7" max="7" width="17.28515625" customWidth="1"/>
@@ -4094,10 +4095,10 @@
         <v>42</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>37</v>
@@ -4120,7 +4121,7 @@
     </row>
     <row r="3" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
-        <f t="shared" ref="A3:A24" si="0">ROW()-2+1000</f>
+        <f t="shared" ref="A3:A25" si="0">ROW()-2+1000</f>
         <v>1001</v>
       </c>
       <c r="B3" s="2">
@@ -4334,13 +4335,13 @@
         <v>9999</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>37</v>
@@ -4370,7 +4371,7 @@
         <v>100110</v>
       </c>
       <c r="C8" s="2">
-        <v>100120</v>
+        <v>100150</v>
       </c>
       <c r="D8" s="2">
         <v>9999</v>
@@ -4382,7 +4383,7 @@
         <v>9999</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>168</v>
+        <v>186</v>
       </c>
       <c r="H8" s="6" t="s">
         <v>54</v>
@@ -4409,147 +4410,147 @@
         <v>88</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="2">
+    <row r="9" spans="1:16" s="19" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="15">
         <f t="shared" si="0"/>
         <v>1007</v>
       </c>
-      <c r="B9" s="2">
+      <c r="B9" s="15">
         <v>100120</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="15">
         <v>100130</v>
       </c>
-      <c r="D9" s="2">
-        <v>9999</v>
-      </c>
-      <c r="E9" s="2">
-        <v>9999</v>
-      </c>
-      <c r="F9" s="2">
-        <v>9999</v>
-      </c>
-      <c r="G9" s="6" t="s">
+      <c r="D9" s="15">
+        <v>9999</v>
+      </c>
+      <c r="E9" s="15">
+        <v>9999</v>
+      </c>
+      <c r="F9" s="15">
+        <v>9999</v>
+      </c>
+      <c r="G9" s="16" t="s">
+        <v>173</v>
+      </c>
+      <c r="H9" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="I9" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="J9" s="17" t="s">
+        <v>172</v>
+      </c>
+      <c r="K9" s="18" t="s">
+        <v>166</v>
+      </c>
+      <c r="L9" s="15">
+        <v>0</v>
+      </c>
+      <c r="M9" s="15">
+        <v>0</v>
+      </c>
+      <c r="O9" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="P9" s="20" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" s="19" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="15">
+        <f t="shared" si="0"/>
+        <v>1008</v>
+      </c>
+      <c r="B10" s="15">
+        <v>100130</v>
+      </c>
+      <c r="C10" s="15">
+        <v>100150</v>
+      </c>
+      <c r="D10" s="15">
+        <v>9999</v>
+      </c>
+      <c r="E10" s="15">
+        <v>9999</v>
+      </c>
+      <c r="F10" s="15">
+        <v>9999</v>
+      </c>
+      <c r="G10" s="16" t="s">
         <v>175</v>
       </c>
-      <c r="H9" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="K9" s="4" t="s">
+      <c r="H10" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="I10" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="J10" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="K10" s="18" t="s">
         <v>166</v>
       </c>
-      <c r="L9" s="2">
-        <v>0</v>
-      </c>
-      <c r="M9" s="2">
-        <v>0</v>
-      </c>
-      <c r="O9" t="b">
-        <v>0</v>
-      </c>
-      <c r="P9" s="14" t="s">
+      <c r="L10" s="15">
+        <v>0</v>
+      </c>
+      <c r="M10" s="15">
+        <v>0</v>
+      </c>
+      <c r="O10" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="P10" s="20" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="2">
-        <f t="shared" si="0"/>
-        <v>1008</v>
-      </c>
-      <c r="B10" s="2">
-        <v>100130</v>
-      </c>
-      <c r="C10" s="2">
+    <row r="11" spans="1:16" s="19" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="15">
+        <f t="shared" si="0"/>
+        <v>1009</v>
+      </c>
+      <c r="B11" s="15">
+        <v>100140</v>
+      </c>
+      <c r="C11" s="15">
         <v>100150</v>
       </c>
-      <c r="D10" s="2">
-        <v>9999</v>
-      </c>
-      <c r="E10" s="2">
-        <v>9999</v>
-      </c>
-      <c r="F10" s="2">
-        <v>9999</v>
-      </c>
-      <c r="G10" s="6" t="s">
+      <c r="D11" s="15">
+        <v>9999</v>
+      </c>
+      <c r="E11" s="15">
+        <v>9999</v>
+      </c>
+      <c r="F11" s="15">
+        <v>9999</v>
+      </c>
+      <c r="G11" s="16" t="s">
         <v>177</v>
       </c>
-      <c r="H10" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="I10" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="J10" s="3" t="s">
+      <c r="H11" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="I11" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="J11" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="K10" s="4" t="s">
+      <c r="K11" s="18" t="s">
         <v>166</v>
       </c>
-      <c r="L10" s="2">
-        <v>0</v>
-      </c>
-      <c r="M10" s="2">
-        <v>0</v>
-      </c>
-      <c r="O10" t="b">
-        <v>0</v>
-      </c>
-      <c r="P10" s="14" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="2">
-        <f t="shared" si="0"/>
-        <v>1009</v>
-      </c>
-      <c r="B11" s="2">
-        <v>100140</v>
-      </c>
-      <c r="C11" s="2">
-        <v>100150</v>
-      </c>
-      <c r="D11" s="2">
-        <v>9999</v>
-      </c>
-      <c r="E11" s="2">
-        <v>9999</v>
-      </c>
-      <c r="F11" s="2">
-        <v>9999</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="H11" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="I11" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="K11" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="L11" s="2">
-        <v>0</v>
-      </c>
-      <c r="M11" s="2">
-        <v>0</v>
-      </c>
-      <c r="O11" t="b">
-        <v>0</v>
-      </c>
-      <c r="P11" s="14" t="s">
+      <c r="L11" s="15">
+        <v>0</v>
+      </c>
+      <c r="M11" s="15">
+        <v>0</v>
+      </c>
+      <c r="O11" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="P11" s="20" t="s">
         <v>88</v>
       </c>
     </row>
@@ -4574,7 +4575,7 @@
         <v>9999</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>54</v>
@@ -4622,7 +4623,7 @@
         <v>9999</v>
       </c>
       <c r="G13" s="16" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="H13" s="16" t="s">
         <v>54</v>
@@ -4670,13 +4671,13 @@
         <v>9999</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>37</v>
@@ -4718,7 +4719,7 @@
         <v>9999</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H15" s="6" t="s">
         <v>54</v>
@@ -4754,7 +4755,7 @@
         <v>100220</v>
       </c>
       <c r="C16" s="2">
-        <v>100400</v>
+        <v>100230</v>
       </c>
       <c r="D16" s="2">
         <v>9999</v>
@@ -4766,7 +4767,7 @@
         <v>9999</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H16" s="6" t="s">
         <v>54</v>
@@ -4799,7 +4800,7 @@
         <v>1015</v>
       </c>
       <c r="B17" s="2">
-        <v>100300</v>
+        <v>100230</v>
       </c>
       <c r="C17" s="2">
         <v>100400</v>
@@ -4814,13 +4815,13 @@
         <v>9999</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>171</v>
+        <v>54</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>171</v>
+        <v>54</v>
       </c>
       <c r="J17" s="3" t="s">
         <v>37</v>
@@ -4841,51 +4842,51 @@
         <v>88</v>
       </c>
     </row>
-    <row r="18" spans="1:16" s="11" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="7">
+    <row r="18" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="2">
         <f t="shared" si="0"/>
         <v>1016</v>
       </c>
-      <c r="B18" s="7">
-        <v>9999</v>
-      </c>
-      <c r="C18" s="7">
-        <v>9999</v>
-      </c>
-      <c r="D18" s="7">
-        <v>10000</v>
-      </c>
-      <c r="E18" s="7">
-        <v>9999</v>
-      </c>
-      <c r="F18" s="7">
-        <v>9999</v>
-      </c>
-      <c r="G18" s="8" t="s">
-        <v>159</v>
-      </c>
-      <c r="H18" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="I18" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="J18" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="K18" s="10" t="s">
+      <c r="B18" s="2">
+        <v>100300</v>
+      </c>
+      <c r="C18" s="2">
+        <v>100400</v>
+      </c>
+      <c r="D18" s="2">
+        <v>9999</v>
+      </c>
+      <c r="E18" s="2">
+        <v>9999</v>
+      </c>
+      <c r="F18" s="2">
+        <v>9999</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="K18" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="L18" s="7">
-        <v>0</v>
-      </c>
-      <c r="M18" s="7">
-        <v>0</v>
-      </c>
-      <c r="O18" s="11" t="b">
-        <v>0</v>
-      </c>
-      <c r="P18" s="13" t="s">
+      <c r="L18" s="2">
+        <v>0</v>
+      </c>
+      <c r="M18" s="2">
+        <v>0</v>
+      </c>
+      <c r="O18" t="b">
+        <v>0</v>
+      </c>
+      <c r="P18" s="14" t="s">
         <v>88</v>
       </c>
     </row>
@@ -4901,7 +4902,7 @@
         <v>9999</v>
       </c>
       <c r="D19" s="7">
-        <v>65</v>
+        <v>10000</v>
       </c>
       <c r="E19" s="7">
         <v>9999</v>
@@ -4910,7 +4911,7 @@
         <v>9999</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>132</v>
+        <v>159</v>
       </c>
       <c r="H19" s="8" t="s">
         <v>54</v>
@@ -4919,7 +4920,7 @@
         <v>54</v>
       </c>
       <c r="J19" s="8" t="s">
-        <v>133</v>
+        <v>95</v>
       </c>
       <c r="K19" s="10" t="s">
         <v>166</v>
@@ -4949,7 +4950,7 @@
         <v>9999</v>
       </c>
       <c r="D20" s="7">
-        <v>10000</v>
+        <v>65</v>
       </c>
       <c r="E20" s="7">
         <v>9999</v>
@@ -4958,7 +4959,7 @@
         <v>9999</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="H20" s="8" t="s">
         <v>54</v>
@@ -4967,7 +4968,7 @@
         <v>54</v>
       </c>
       <c r="J20" s="8" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="K20" s="10" t="s">
         <v>166</v>
@@ -4985,147 +4986,147 @@
         <v>88</v>
       </c>
     </row>
-    <row r="21" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="2">
+    <row r="21" spans="1:16" s="11" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="7">
         <f t="shared" si="0"/>
         <v>1019</v>
       </c>
-      <c r="B21" s="2">
+      <c r="B21" s="7">
+        <v>9999</v>
+      </c>
+      <c r="C21" s="7">
+        <v>9999</v>
+      </c>
+      <c r="D21" s="7">
+        <v>10000</v>
+      </c>
+      <c r="E21" s="7">
+        <v>9999</v>
+      </c>
+      <c r="F21" s="7">
+        <v>9999</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="I21" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="J21" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="K21" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="L21" s="7">
+        <v>0</v>
+      </c>
+      <c r="M21" s="7">
+        <v>0</v>
+      </c>
+      <c r="O21" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="P21" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="2">
+        <f t="shared" si="0"/>
+        <v>1020</v>
+      </c>
+      <c r="B22" s="2">
         <v>100400</v>
       </c>
-      <c r="C21" s="2">
+      <c r="C22" s="2">
         <v>100420</v>
       </c>
-      <c r="D21" s="2">
-        <v>9999</v>
-      </c>
-      <c r="E21" s="2">
-        <v>9999</v>
-      </c>
-      <c r="F21" s="2">
-        <v>9999</v>
-      </c>
-      <c r="G21" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="H21" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="I21" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="J21" s="3" t="s">
+      <c r="D22" s="2">
+        <v>9999</v>
+      </c>
+      <c r="E22" s="2">
+        <v>9999</v>
+      </c>
+      <c r="F22" s="2">
+        <v>9999</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="J22" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="K21" s="4" t="s">
+      <c r="K22" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="L21" s="2">
-        <v>0</v>
-      </c>
-      <c r="M21" s="2">
-        <v>0</v>
-      </c>
-      <c r="O21" t="b">
-        <v>0</v>
-      </c>
-      <c r="P21" s="14" t="s">
+      <c r="L22" s="2">
+        <v>0</v>
+      </c>
+      <c r="M22" s="2">
+        <v>0</v>
+      </c>
+      <c r="O22" t="b">
+        <v>0</v>
+      </c>
+      <c r="P22" s="14" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="22" spans="1:16" s="19" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="15">
-        <f t="shared" si="0"/>
-        <v>1020</v>
-      </c>
-      <c r="B22" s="15">
+    <row r="23" spans="1:16" s="19" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="15">
+        <f t="shared" si="0"/>
+        <v>1021</v>
+      </c>
+      <c r="B23" s="15">
         <v>100410</v>
       </c>
-      <c r="C22" s="15">
+      <c r="C23" s="15">
         <v>100420</v>
       </c>
-      <c r="D22" s="15">
-        <v>9999</v>
-      </c>
-      <c r="E22" s="15">
-        <v>9999</v>
-      </c>
-      <c r="F22" s="15">
-        <v>9999</v>
-      </c>
-      <c r="G22" s="16" t="s">
-        <v>176</v>
-      </c>
-      <c r="H22" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="I22" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="J22" s="17" t="s">
+      <c r="D23" s="15">
+        <v>9999</v>
+      </c>
+      <c r="E23" s="15">
+        <v>9999</v>
+      </c>
+      <c r="F23" s="15">
+        <v>9999</v>
+      </c>
+      <c r="G23" s="16" t="s">
+        <v>174</v>
+      </c>
+      <c r="H23" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="I23" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="J23" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="K22" s="18" t="s">
+      <c r="K23" s="18" t="s">
         <v>166</v>
       </c>
-      <c r="L22" s="15">
-        <v>0</v>
-      </c>
-      <c r="M22" s="15">
-        <v>0</v>
-      </c>
-      <c r="O22" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="P22" s="20" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="2">
-        <f t="shared" si="0"/>
-        <v>1021</v>
-      </c>
-      <c r="B23" s="2">
-        <v>100420</v>
-      </c>
-      <c r="C23" s="2">
-        <v>100500</v>
-      </c>
-      <c r="D23" s="2">
-        <v>9999</v>
-      </c>
-      <c r="E23" s="2">
-        <v>9999</v>
-      </c>
-      <c r="F23" s="2">
-        <v>9999</v>
-      </c>
-      <c r="G23" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="H23" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="I23" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="K23" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="L23" s="2">
-        <v>0</v>
-      </c>
-      <c r="M23" s="2">
-        <v>0</v>
-      </c>
-      <c r="O23" t="b">
-        <v>0</v>
-      </c>
-      <c r="P23" s="14" t="s">
+      <c r="L23" s="15">
+        <v>0</v>
+      </c>
+      <c r="M23" s="15">
+        <v>0</v>
+      </c>
+      <c r="O23" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="P23" s="20" t="s">
         <v>88</v>
       </c>
     </row>
@@ -5135,11 +5136,11 @@
         <v>1022</v>
       </c>
       <c r="B24" s="2">
+        <v>100420</v>
+      </c>
+      <c r="C24" s="2">
         <v>100500</v>
       </c>
-      <c r="C24" s="2">
-        <v>9999</v>
-      </c>
       <c r="D24" s="2">
         <v>9999</v>
       </c>
@@ -5150,31 +5151,79 @@
         <v>9999</v>
       </c>
       <c r="G24" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="I24" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="K24" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="L24" s="2">
+        <v>0</v>
+      </c>
+      <c r="M24" s="2">
+        <v>0</v>
+      </c>
+      <c r="O24" t="b">
+        <v>0</v>
+      </c>
+      <c r="P24" s="14" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="2">
+        <f t="shared" si="0"/>
+        <v>1023</v>
+      </c>
+      <c r="B25" s="2">
+        <v>100500</v>
+      </c>
+      <c r="C25" s="2">
+        <v>9999</v>
+      </c>
+      <c r="D25" s="2">
+        <v>9999</v>
+      </c>
+      <c r="E25" s="2">
+        <v>9999</v>
+      </c>
+      <c r="F25" s="2">
+        <v>9999</v>
+      </c>
+      <c r="G25" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="H24" s="6" t="s">
+      <c r="H25" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="I24" s="6" t="s">
+      <c r="I25" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="J24" s="3" t="s">
+      <c r="J25" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="K24" s="4" t="s">
+      <c r="K25" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="L24" s="2">
-        <v>0</v>
-      </c>
-      <c r="M24" s="2">
-        <v>0</v>
-      </c>
-      <c r="N24" s="5"/>
-      <c r="O24" t="b">
-        <v>0</v>
-      </c>
-      <c r="P24" s="14" t="s">
+      <c r="L25" s="2">
+        <v>0</v>
+      </c>
+      <c r="M25" s="2">
+        <v>0</v>
+      </c>
+      <c r="N25" s="5"/>
+      <c r="O25" t="b">
+        <v>0</v>
+      </c>
+      <c r="P25" s="14" t="s">
         <v>74</v>
       </c>
     </row>
